--- a/Modelo_España_Portugal/Resultados/ES_PT_Unidos.xlsx
+++ b/Modelo_España_Portugal/Resultados/ES_PT_Unidos.xlsx
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>41635571196.58096</v>
+        <v>41645878125.87338</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3934,31 +3934,31 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>14990.09405714286</v>
+        <v>14990.09508278388</v>
       </c>
       <c r="D2" t="n">
-        <v>8493.769982857144</v>
+        <v>8493.768957216116</v>
       </c>
       <c r="E2" t="n">
         <v>-0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>3083.729786430806</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>1898.210045714286</v>
+        <v>1898.209045714286</v>
       </c>
       <c r="I2" t="n">
-        <v>2209.497954285714</v>
+        <v>2209.498954285714</v>
       </c>
       <c r="J2" t="n">
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0.0007179487180017019</v>
       </c>
     </row>
     <row r="3">
@@ -3981,7 +3981,7 @@
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>1682.805794645323</v>
       </c>
       <c r="H3" t="n">
         <v>1898.210045714286</v>
@@ -4016,7 +4016,7 @@
         <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>3083.73745112773</v>
+        <v>3837</v>
       </c>
       <c r="H4" t="n">
         <v>1898.210045714286</v>
@@ -4051,7 +4051,7 @@
         <v>-0</v>
       </c>
       <c r="G5" t="n">
-        <v>3837</v>
+        <v>3558.493469009316</v>
       </c>
       <c r="H5" t="n">
         <v>1898.210045714286</v>
@@ -4144,10 +4144,10 @@
         <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>24395.85876</v>
+        <v>15079.8655</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>9315.993259999999</v>
       </c>
       <c r="E8" t="n">
         <v>-0</v>
@@ -4191,7 +4191,7 @@
         <v>-0</v>
       </c>
       <c r="G9" t="n">
-        <v>2531.99449119479</v>
+        <v>2845.60919542915</v>
       </c>
       <c r="H9" t="n">
         <v>2310.658367142858</v>
@@ -4599,10 +4599,10 @@
         <v>-0</v>
       </c>
       <c r="C21" t="n">
-        <v>24585.85766</v>
+        <v>17079.64903553114</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>7506.208624468865</v>
       </c>
       <c r="E21" t="n">
         <v>1357</v>
@@ -4961,7 +4961,7 @@
         <v>-0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0</v>
+        <v>2664.321220063812</v>
       </c>
       <c r="H31" t="n">
         <v>1987.516924285714</v>
@@ -5346,7 +5346,7 @@
         <v>-0</v>
       </c>
       <c r="G42" t="n">
-        <v>3392.596677652512</v>
+        <v>171.1100635471794</v>
       </c>
       <c r="H42" t="n">
         <v>2399.965247142857</v>
@@ -5451,7 +5451,7 @@
         <v>-0</v>
       </c>
       <c r="G45" t="n">
-        <v>-0</v>
+        <v>3788.62482270569</v>
       </c>
       <c r="H45" t="n">
         <v>2179.010788571429</v>
@@ -5521,7 +5521,7 @@
         <v>-0</v>
       </c>
       <c r="G47" t="n">
-        <v>3837</v>
+        <v>3200.386399344846</v>
       </c>
       <c r="H47" t="n">
         <v>1921.230587142857</v>
@@ -5556,7 +5556,7 @@
         <v>-0</v>
       </c>
       <c r="G48" t="n">
-        <v>3837</v>
+        <v>2954.536567774185</v>
       </c>
       <c r="H48" t="n">
         <v>1847.579101428571</v>
@@ -5964,10 +5964,10 @@
         <v>-0</v>
       </c>
       <c r="C60" t="n">
-        <v>21773.87394</v>
+        <v>15102.30835714286</v>
       </c>
       <c r="D60" t="n">
-        <v>-0</v>
+        <v>6671.56558285714</v>
       </c>
       <c r="E60" t="n">
         <v>-0</v>
@@ -6253,7 +6253,7 @@
         <v>-0</v>
       </c>
       <c r="F68" t="n">
-        <v>7148.066353688082</v>
+        <v>7604.9</v>
       </c>
       <c r="G68" t="n">
         <v>-0</v>
@@ -6288,7 +6288,7 @@
         <v>-0</v>
       </c>
       <c r="F69" t="n">
-        <v>6028.163934888532</v>
+        <v>5571.330288576614</v>
       </c>
       <c r="G69" t="n">
         <v>-0</v>
@@ -6431,7 +6431,7 @@
         <v>-0</v>
       </c>
       <c r="G73" t="n">
-        <v>-0</v>
+        <v>1569.870594003095</v>
       </c>
       <c r="H73" t="n">
         <v>1678.307154285714</v>
@@ -6466,7 +6466,7 @@
         <v>-0</v>
       </c>
       <c r="G74" t="n">
-        <v>938.1320131615357</v>
+        <v>2545.132013161536</v>
       </c>
       <c r="H74" t="n">
         <v>1683.759498571429</v>
@@ -6711,7 +6711,7 @@
         <v>-0</v>
       </c>
       <c r="G81" t="n">
-        <v>2214.346245157625</v>
+        <v>3837</v>
       </c>
       <c r="H81" t="n">
         <v>2096.20782</v>
@@ -6746,7 +6746,7 @@
         <v>-0</v>
       </c>
       <c r="G82" t="n">
-        <v>1525.289301498133</v>
+        <v>-0</v>
       </c>
       <c r="H82" t="n">
         <v>2236.145644285714</v>
@@ -6781,7 +6781,7 @@
         <v>-0</v>
       </c>
       <c r="G83" t="n">
-        <v>1087.155534643317</v>
+        <v>-0</v>
       </c>
       <c r="H83" t="n">
         <v>2236.145644285714</v>
@@ -7128,7 +7128,7 @@
         <v>-0</v>
       </c>
       <c r="F93" t="n">
-        <v>6095.794777803401</v>
+        <v>7604.9</v>
       </c>
       <c r="G93" t="n">
         <v>-0</v>
@@ -7233,7 +7233,7 @@
         <v>-0</v>
       </c>
       <c r="F96" t="n">
-        <v>2753.729489753548</v>
+        <v>1244.624267556949</v>
       </c>
       <c r="G96" t="n">
         <v>-0</v>
@@ -7306,7 +7306,7 @@
         <v>-0</v>
       </c>
       <c r="G98" t="n">
-        <v>1734.634062370035</v>
+        <v>3341.634062370035</v>
       </c>
       <c r="H98" t="n">
         <v>1798.388448571429</v>
@@ -8146,7 +8146,7 @@
         <v>-0</v>
       </c>
       <c r="G122" t="n">
-        <v>1555.808003591325</v>
+        <v>38.17587268166244</v>
       </c>
       <c r="H122" t="n">
         <v>2371.599285714286</v>
@@ -8181,7 +8181,7 @@
         <v>-0</v>
       </c>
       <c r="G123" t="n">
-        <v>358.0781236013381</v>
+        <v>2581.962582769962</v>
       </c>
       <c r="H123" t="n">
         <v>2371.599285714286</v>
@@ -8321,7 +8321,7 @@
         <v>-0</v>
       </c>
       <c r="G127" t="n">
-        <v>3830.884459168623</v>
+        <v>-0</v>
       </c>
       <c r="H127" t="n">
         <v>2371.599285714286</v>
@@ -8659,10 +8659,10 @@
         <v>-0</v>
       </c>
       <c r="C137" t="n">
-        <v>29362.5473</v>
+        <v>15076.83301428572</v>
       </c>
       <c r="D137" t="n">
-        <v>12779.20872</v>
+        <v>27064.92300571428</v>
       </c>
       <c r="E137" t="n">
         <v>-0</v>
@@ -8703,7 +8703,7 @@
         <v>-0</v>
       </c>
       <c r="F138" t="n">
-        <v>5461.699245228119</v>
+        <v>3061.699245228117</v>
       </c>
       <c r="G138" t="n">
         <v>-0</v>
@@ -8843,7 +8843,7 @@
         <v>-0</v>
       </c>
       <c r="F142" t="n">
-        <v>5121.321697167798</v>
+        <v>7521.321697167798</v>
       </c>
       <c r="G142" t="n">
         <v>-0</v>
@@ -9053,7 +9053,7 @@
         <v>-0</v>
       </c>
       <c r="F148" t="n">
-        <v>1254.120081118349</v>
+        <v>-0</v>
       </c>
       <c r="G148" t="n">
         <v>-0</v>
@@ -9079,10 +9079,10 @@
         <v>-0</v>
       </c>
       <c r="C149" t="n">
-        <v>18274.85901008463</v>
+        <v>14986.28471135531</v>
       </c>
       <c r="D149" t="n">
-        <v>14518.95112991537</v>
+        <v>17807.52542864469</v>
       </c>
       <c r="E149" t="n">
         <v>-0</v>
@@ -9123,7 +9123,7 @@
         <v>-0</v>
       </c>
       <c r="F150" t="n">
-        <v>795.7164574239072</v>
+        <v>2403.586865048359</v>
       </c>
       <c r="G150" t="n">
         <v>-0</v>
@@ -9193,7 +9193,7 @@
         <v>-0</v>
       </c>
       <c r="F152" t="n">
-        <v>658.594417483028</v>
+        <v>3819.657035759352</v>
       </c>
       <c r="G152" t="n">
         <v>-0</v>
@@ -9228,7 +9228,7 @@
         <v>-0</v>
       </c>
       <c r="F153" t="n">
-        <v>7604.9</v>
+        <v>4090.087055217573</v>
       </c>
       <c r="G153" t="n">
         <v>-0</v>
@@ -9674,10 +9674,10 @@
         <v>-0</v>
       </c>
       <c r="C166" t="n">
-        <v>15054.19568571429</v>
+        <v>18350.68925462697</v>
       </c>
       <c r="D166" t="n">
-        <v>11241.65207428571</v>
+        <v>7945.15850537303</v>
       </c>
       <c r="E166" t="n">
         <v>-0</v>
@@ -9709,10 +9709,10 @@
         <v>-0</v>
       </c>
       <c r="C167" t="n">
-        <v>15031.55835714286</v>
+        <v>26713.84534</v>
       </c>
       <c r="D167" t="n">
-        <v>11682.28698285714</v>
+        <v>-0</v>
       </c>
       <c r="E167" t="n">
         <v>-0</v>
@@ -9744,10 +9744,10 @@
         <v>-0</v>
       </c>
       <c r="C168" t="n">
-        <v>14986.28368571428</v>
+        <v>26789.8449</v>
       </c>
       <c r="D168" t="n">
-        <v>11803.56121428571</v>
+        <v>-0</v>
       </c>
       <c r="E168" t="n">
         <v>-0</v>
@@ -9776,13 +9776,13 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>-0</v>
+        <v>2672.151971428575</v>
       </c>
       <c r="C169" t="n">
-        <v>14986.28368571428</v>
+        <v>26599.846</v>
       </c>
       <c r="D169" t="n">
-        <v>11613.56231428571</v>
+        <v>-0</v>
       </c>
       <c r="E169" t="n">
         <v>-0</v>
@@ -9791,7 +9791,7 @@
         <v>-0</v>
       </c>
       <c r="G169" t="n">
-        <v>741.366579102968</v>
+        <v>-0</v>
       </c>
       <c r="H169" t="n">
         <v>2411.225921428571</v>
@@ -9880,31 +9880,31 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-10493.06584</v>
+        <v>-10493.06655794872</v>
       </c>
       <c r="D2" t="n">
-        <v>-8493.769982857144</v>
+        <v>-8493.768957216116</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-2621.170318466185</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1328.747032</v>
+        <v>-1328.746332</v>
       </c>
       <c r="I2" t="n">
-        <v>-2209.497954285714</v>
+        <v>-2209.498954285714</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0.0007000000000516593</v>
       </c>
     </row>
     <row r="3">
@@ -9927,7 +9927,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-1262.104345983993</v>
       </c>
       <c r="H3" t="n">
         <v>-1328.747032</v>
@@ -9962,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-2312.803088345798</v>
+        <v>-2877.75</v>
       </c>
       <c r="H4" t="n">
         <v>-1328.747032</v>
@@ -9997,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-2877.75</v>
+        <v>-2668.870101756987</v>
       </c>
       <c r="H5" t="n">
         <v>-1328.747032</v>
@@ -10090,10 +10090,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-17077.101132</v>
+        <v>-10555.90585</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-9315.993259999999</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10137,7 +10137,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-1898.995868396093</v>
+        <v>-2134.206896571862</v>
       </c>
       <c r="H9" t="n">
         <v>-1617.460857</v>
@@ -10545,10 +10545,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>-17210.100362</v>
+        <v>-11955.75432487179</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-7506.208624468865</v>
       </c>
       <c r="E21" t="n">
         <v>-787.0599999999999</v>
@@ -10907,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-1998.240915047859</v>
       </c>
       <c r="H31" t="n">
         <v>-1391.261847</v>
@@ -11292,7 +11292,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>-2544.447508239384</v>
+        <v>-128.3325476603845</v>
       </c>
       <c r="H42" t="n">
         <v>-1679.975673</v>
@@ -11397,7 +11397,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-2841.468617029268</v>
       </c>
       <c r="H45" t="n">
         <v>-1525.307552</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>-2877.75</v>
+        <v>-2400.289799508634</v>
       </c>
       <c r="H47" t="n">
         <v>-1344.861411</v>
@@ -11502,7 +11502,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>-2877.75</v>
+        <v>-2215.902425830639</v>
       </c>
       <c r="H48" t="n">
         <v>-1293.305371</v>
@@ -11910,10 +11910,10 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>-15241.711758</v>
+        <v>-10571.61585</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>-6671.56558285714</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -12199,7 +12199,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>-6075.85640063487</v>
+        <v>-6464.165</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -12234,7 +12234,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>-5123.939344655252</v>
+        <v>-4735.630745290122</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -12377,7 +12377,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-1177.402945502321</v>
       </c>
       <c r="H73" t="n">
         <v>-1174.815008</v>
@@ -12412,7 +12412,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>-703.5990098711518</v>
+        <v>-1908.849009871152</v>
       </c>
       <c r="H74" t="n">
         <v>-1178.631649</v>
@@ -12657,7 +12657,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>-1660.759683868219</v>
+        <v>-2877.75</v>
       </c>
       <c r="H81" t="n">
         <v>-1467.345474</v>
@@ -12692,7 +12692,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>-1143.9669761236</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>-1565.301951</v>
@@ -12727,7 +12727,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>-815.3666509824874</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>-1565.301951</v>
@@ -13074,7 +13074,7 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>-5181.425561132891</v>
+        <v>-6464.165</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -13179,7 +13179,7 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>-2340.670066290516</v>
+        <v>-1057.930627423407</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -13252,7 +13252,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>-1300.975546777526</v>
+        <v>-2506.225546777526</v>
       </c>
       <c r="H98" t="n">
         <v>-1258.871914</v>
@@ -14092,7 +14092,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>-1166.856002693494</v>
+        <v>-28.63190451124683</v>
       </c>
       <c r="H122" t="n">
         <v>-1660.1195</v>
@@ -14127,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>-268.5585927010036</v>
+        <v>-1936.471937077471</v>
       </c>
       <c r="H123" t="n">
         <v>-1660.1195</v>
@@ -14267,7 +14267,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>-2873.163344376467</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
         <v>-1660.1195</v>
@@ -14605,10 +14605,10 @@
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>-20553.78311</v>
+        <v>-10553.78311</v>
       </c>
       <c r="D137" t="n">
-        <v>-12779.20872</v>
+        <v>-27064.92300571428</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -14649,7 +14649,7 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>-4642.444358443901</v>
+        <v>-2602.4443584439</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -14789,7 +14789,7 @@
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>-4353.123442592629</v>
+        <v>-6393.123442592629</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14999,7 +14999,7 @@
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>-1066.002068950597</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -15025,10 +15025,10 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>-12792.40130705924</v>
+        <v>-10490.39929794872</v>
       </c>
       <c r="D149" t="n">
-        <v>-14518.95112991537</v>
+        <v>-17807.52542864469</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -15069,7 +15069,7 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>-676.3589888103211</v>
+        <v>-2043.048835291105</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -15139,7 +15139,7 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>-559.8052548605738</v>
+        <v>-3246.708480395449</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -15174,7 +15174,7 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>-6464.165</v>
+        <v>-3476.573996934937</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -15620,10 +15620,10 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>-10537.93698</v>
+        <v>-12845.48247823888</v>
       </c>
       <c r="D166" t="n">
-        <v>-11241.65207428571</v>
+        <v>-7945.15850537303</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -15655,10 +15655,10 @@
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>-10522.09085</v>
+        <v>-18699.691738</v>
       </c>
       <c r="D167" t="n">
-        <v>-11682.28698285714</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -15690,10 +15690,10 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>-10490.39858</v>
+        <v>-18752.89143</v>
       </c>
       <c r="D168" t="n">
-        <v>-11803.56121428571</v>
+        <v>0</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -15722,13 +15722,13 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>-1870.506380000002</v>
       </c>
       <c r="C169" t="n">
-        <v>-10490.39858</v>
+        <v>-18619.8922</v>
       </c>
       <c r="D169" t="n">
-        <v>-11613.56231428571</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -15737,7 +15737,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>-556.024934327226</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
         <v>-1687.858145</v>
@@ -15794,7 +15794,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -15808,7 +15808,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1066.877253106629</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4">
@@ -15822,7 +15822,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1453.122746893371</v>
+        <v>2206.385295765641</v>
       </c>
     </row>
     <row r="5">
@@ -15875,7 +15875,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-6521.195282000001</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>319.8214532803145</v>
@@ -15892,7 +15892,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>692.3488473322468</v>
+        <v>1005.963551566606</v>
       </c>
     </row>
     <row r="10">
@@ -16032,7 +16032,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -16046,7 +16046,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2040.000000000002</v>
       </c>
     </row>
     <row r="21">
@@ -16057,10 +16057,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>-5254.346037128205</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="22">
@@ -16074,7 +16074,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2289.77724936156</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="23">
@@ -16088,7 +16088,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="24">
@@ -16102,7 +16102,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -16116,7 +16116,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>2750.22275063844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -16158,7 +16158,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-307.9580782624947</v>
+        <v>-921.9131470305449</v>
       </c>
     </row>
     <row r="29">
@@ -16172,7 +16172,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-1880.738493410195</v>
+        <v>-1306.191449662139</v>
       </c>
     </row>
     <row r="30">
@@ -16186,7 +16186,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-1982.086804956182</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="31">
@@ -16200,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-1057.321220063812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -16354,7 +16354,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1614.486614105333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -16382,7 +16382,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>2961.591467568281</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="45">
@@ -16396,7 +16396,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>818.3751772943097</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="46">
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>31.0668596230762</v>
       </c>
     </row>
     <row r="47">
@@ -16424,7 +16424,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>2645.546741032078</v>
+        <v>2008.933140376924</v>
       </c>
     </row>
     <row r="48">
@@ -16603,10 +16603,10 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>-4670.095907999998</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>-1043.478260869565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -16620,7 +16620,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>-1043.478260869565</v>
       </c>
     </row>
     <row r="62">
@@ -16718,7 +16718,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>3000</v>
+        <v>2611.691400634869</v>
       </c>
     </row>
     <row r="69">
@@ -16732,7 +16732,7 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>1611.131026371008</v>
+        <v>1999.439625736138</v>
       </c>
     </row>
     <row r="70">
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>768.4141138996788</v>
       </c>
     </row>
     <row r="82">
@@ -16914,7 +16914,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>81.71069850186632</v>
       </c>
     </row>
     <row r="83">
@@ -16928,7 +16928,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>850.1248124015451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -17068,7 +17068,7 @@
         <v>6352.198303053638</v>
       </c>
       <c r="D93" t="n">
-        <v>2469.93727723199</v>
+        <v>1187.197838364881</v>
       </c>
     </row>
     <row r="94">
@@ -17110,7 +17110,7 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1282.739438867109</v>
       </c>
     </row>
     <row r="97">
@@ -17278,7 +17278,7 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>-1043.478260869565</v>
       </c>
     </row>
     <row r="109">
@@ -17292,7 +17292,7 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>-1043.478260869565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -17390,7 +17390,7 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>2040</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="117">
@@ -17404,7 +17404,7 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>3000</v>
+        <v>1875.948512604863</v>
       </c>
     </row>
     <row r="118">
@@ -17432,7 +17432,7 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>164.0514873951367</v>
       </c>
     </row>
     <row r="120">
@@ -17488,7 +17488,7 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>-2410.563041633822</v>
+        <v>-186.6785824651985</v>
       </c>
     </row>
     <row r="124">
@@ -17544,7 +17544,7 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>-2223.884459168623</v>
       </c>
     </row>
     <row r="128">
@@ -17614,7 +17614,7 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>-1043.478260869565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -17628,7 +17628,7 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>-1043.478260869565</v>
       </c>
     </row>
     <row r="134">
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
         <v>-3000</v>
@@ -17698,7 +17698,7 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>2040.000000000002</v>
       </c>
     </row>
     <row r="139">
@@ -17754,7 +17754,7 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>2040</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -17838,7 +17838,7 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1066.002068950597</v>
       </c>
     </row>
     <row r="149">
@@ -17849,7 +17849,7 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>-2302.002009110525</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -17866,7 +17866,7 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>1366.689846480784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -17894,7 +17894,7 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>3000</v>
+        <v>313.0967744651247</v>
       </c>
     </row>
     <row r="153">
@@ -17908,7 +17908,7 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>12.40899693493702</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="154">
@@ -18087,7 +18087,7 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>-2307.545498238876</v>
       </c>
       <c r="D166" t="n">
         <v>289.7566376394398</v>
@@ -18101,7 +18101,7 @@
         <v>-6159.181570317094</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>-8177.600887999997</v>
       </c>
       <c r="D167" t="n">
         <v>-523.9108551198524</v>
@@ -18115,7 +18115,7 @@
         <v>-26698.52</v>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>-8262.492849999997</v>
       </c>
       <c r="D168" t="n">
         <v>-1262.262266470148</v>
@@ -18129,7 +18129,7 @@
         <v>-26698.52</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="D169" t="n">
         <v>-2667.698142161701</v>
@@ -18177,7 +18177,7 @@
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>3000</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -18191,7 +18191,7 @@
         <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>1066.877253106629</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4">
@@ -18205,7 +18205,7 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>1453.122746893371</v>
+        <v>2206.385295765641</v>
       </c>
     </row>
     <row r="5">
@@ -18275,7 +18275,7 @@
         <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>692.3488473322468</v>
+        <v>1005.963551566606</v>
       </c>
     </row>
     <row r="10">
@@ -18415,7 +18415,7 @@
         <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>3000</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -18429,7 +18429,7 @@
         <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0</v>
+        <v>2040.000000000002</v>
       </c>
     </row>
     <row r="21">
@@ -18443,7 +18443,7 @@
         <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="22">
@@ -18457,7 +18457,7 @@
         <v>-0</v>
       </c>
       <c r="D22" t="n">
-        <v>2289.77724936156</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="23">
@@ -18471,7 +18471,7 @@
         <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="24">
@@ -18485,7 +18485,7 @@
         <v>-0</v>
       </c>
       <c r="D24" t="n">
-        <v>3000</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -18499,7 +18499,7 @@
         <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>2750.22275063844</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -18737,7 +18737,7 @@
         <v>-0</v>
       </c>
       <c r="D42" t="n">
-        <v>1614.486614105333</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="43">
@@ -18765,7 +18765,7 @@
         <v>-0</v>
       </c>
       <c r="D44" t="n">
-        <v>2961.591467568281</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="45">
@@ -18779,7 +18779,7 @@
         <v>-0</v>
       </c>
       <c r="D45" t="n">
-        <v>818.3751772943097</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="46">
@@ -18793,7 +18793,7 @@
         <v>-0</v>
       </c>
       <c r="D46" t="n">
-        <v>-0</v>
+        <v>31.0668596230762</v>
       </c>
     </row>
     <row r="47">
@@ -18807,7 +18807,7 @@
         <v>-0</v>
       </c>
       <c r="D47" t="n">
-        <v>2645.546741032078</v>
+        <v>2008.933140376924</v>
       </c>
     </row>
     <row r="48">
@@ -19101,7 +19101,7 @@
         <v>-0</v>
       </c>
       <c r="D68" t="n">
-        <v>3000</v>
+        <v>2611.691400634869</v>
       </c>
     </row>
     <row r="69">
@@ -19115,7 +19115,7 @@
         <v>-0</v>
       </c>
       <c r="D69" t="n">
-        <v>1611.131026371008</v>
+        <v>1999.439625736138</v>
       </c>
     </row>
     <row r="70">
@@ -19283,7 +19283,7 @@
         <v>-0</v>
       </c>
       <c r="D81" t="n">
-        <v>-0</v>
+        <v>768.4141138996788</v>
       </c>
     </row>
     <row r="82">
@@ -19297,7 +19297,7 @@
         <v>-0</v>
       </c>
       <c r="D82" t="n">
-        <v>-0</v>
+        <v>81.71069850186632</v>
       </c>
     </row>
     <row r="83">
@@ -19311,7 +19311,7 @@
         <v>-0</v>
       </c>
       <c r="D83" t="n">
-        <v>850.1248124015451</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="84">
@@ -19451,7 +19451,7 @@
         <v>6352.198303053638</v>
       </c>
       <c r="D93" t="n">
-        <v>2469.93727723199</v>
+        <v>1187.197838364881</v>
       </c>
     </row>
     <row r="94">
@@ -19493,7 +19493,7 @@
         <v>-0</v>
       </c>
       <c r="D96" t="n">
-        <v>-0</v>
+        <v>1282.739438867109</v>
       </c>
     </row>
     <row r="97">
@@ -19773,7 +19773,7 @@
         <v>-0</v>
       </c>
       <c r="D116" t="n">
-        <v>2040</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="117">
@@ -19787,7 +19787,7 @@
         <v>-0</v>
       </c>
       <c r="D117" t="n">
-        <v>3000</v>
+        <v>1875.948512604863</v>
       </c>
     </row>
     <row r="118">
@@ -19815,7 +19815,7 @@
         <v>-0</v>
       </c>
       <c r="D119" t="n">
-        <v>-0</v>
+        <v>164.0514873951367</v>
       </c>
     </row>
     <row r="120">
@@ -20081,7 +20081,7 @@
         <v>-0</v>
       </c>
       <c r="D138" t="n">
-        <v>-0</v>
+        <v>2040.000000000002</v>
       </c>
     </row>
     <row r="139">
@@ -20137,7 +20137,7 @@
         <v>-0</v>
       </c>
       <c r="D142" t="n">
-        <v>2040</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="143">
@@ -20221,7 +20221,7 @@
         <v>-0</v>
       </c>
       <c r="D148" t="n">
-        <v>-0</v>
+        <v>1066.002068950597</v>
       </c>
     </row>
     <row r="149">
@@ -20249,7 +20249,7 @@
         <v>-0</v>
       </c>
       <c r="D150" t="n">
-        <v>1366.689846480784</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="151">
@@ -20277,7 +20277,7 @@
         <v>-0</v>
       </c>
       <c r="D152" t="n">
-        <v>3000</v>
+        <v>313.0967744651247</v>
       </c>
     </row>
     <row r="153">
@@ -20291,7 +20291,7 @@
         <v>-0</v>
       </c>
       <c r="D153" t="n">
-        <v>12.40899693493702</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="154">
@@ -20641,7 +20641,7 @@
         <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>6521.195282000001</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>-0</v>
@@ -20823,7 +20823,7 @@
         <v>-0</v>
       </c>
       <c r="C21" t="n">
-        <v>5254.346037128205</v>
+        <v>-0</v>
       </c>
       <c r="D21" t="n">
         <v>-0</v>
@@ -20924,7 +20924,7 @@
         <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>307.9580782624947</v>
+        <v>921.9131470305449</v>
       </c>
     </row>
     <row r="29">
@@ -20938,7 +20938,7 @@
         <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>1880.738493410195</v>
+        <v>1306.191449662139</v>
       </c>
     </row>
     <row r="30">
@@ -20952,7 +20952,7 @@
         <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>1982.086804956182</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="31">
@@ -20966,7 +20966,7 @@
         <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>1057.321220063812</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -21369,10 +21369,10 @@
         <v>-0</v>
       </c>
       <c r="C60" t="n">
-        <v>4670.095907999998</v>
+        <v>-0</v>
       </c>
       <c r="D60" t="n">
-        <v>1043.478260869565</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="61">
@@ -21386,7 +21386,7 @@
         <v>-0</v>
       </c>
       <c r="D61" t="n">
-        <v>-0</v>
+        <v>1043.478260869565</v>
       </c>
     </row>
     <row r="62">
@@ -22044,7 +22044,7 @@
         <v>-0</v>
       </c>
       <c r="D108" t="n">
-        <v>-0</v>
+        <v>1043.478260869565</v>
       </c>
     </row>
     <row r="109">
@@ -22058,7 +22058,7 @@
         <v>-0</v>
       </c>
       <c r="D109" t="n">
-        <v>1043.478260869565</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="110">
@@ -22254,7 +22254,7 @@
         <v>-0</v>
       </c>
       <c r="D123" t="n">
-        <v>2410.563041633822</v>
+        <v>186.6785824651985</v>
       </c>
     </row>
     <row r="124">
@@ -22310,7 +22310,7 @@
         <v>-0</v>
       </c>
       <c r="D127" t="n">
-        <v>-0</v>
+        <v>2223.884459168623</v>
       </c>
     </row>
     <row r="128">
@@ -22380,7 +22380,7 @@
         <v>-0</v>
       </c>
       <c r="D132" t="n">
-        <v>1043.478260869565</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="133">
@@ -22394,7 +22394,7 @@
         <v>-0</v>
       </c>
       <c r="D133" t="n">
-        <v>-0</v>
+        <v>1043.478260869565</v>
       </c>
     </row>
     <row r="134">
@@ -22447,7 +22447,7 @@
         <v>-0</v>
       </c>
       <c r="C137" t="n">
-        <v>10000</v>
+        <v>-0</v>
       </c>
       <c r="D137" t="n">
         <v>3000</v>
@@ -22615,7 +22615,7 @@
         <v>-0</v>
       </c>
       <c r="C149" t="n">
-        <v>2302.002009110525</v>
+        <v>-0</v>
       </c>
       <c r="D149" t="n">
         <v>-0</v>
@@ -22853,7 +22853,7 @@
         <v>-0</v>
       </c>
       <c r="C166" t="n">
-        <v>-0</v>
+        <v>2307.545498238876</v>
       </c>
       <c r="D166" t="n">
         <v>-0</v>
@@ -22867,7 +22867,7 @@
         <v>6159.181570317094</v>
       </c>
       <c r="C167" t="n">
-        <v>-0</v>
+        <v>8177.600887999997</v>
       </c>
       <c r="D167" t="n">
         <v>523.9108551198524</v>
@@ -22881,7 +22881,7 @@
         <v>26698.52</v>
       </c>
       <c r="C168" t="n">
-        <v>-0</v>
+        <v>8262.492849999997</v>
       </c>
       <c r="D168" t="n">
         <v>1262.262266470148</v>
@@ -22895,7 +22895,7 @@
         <v>26698.52</v>
       </c>
       <c r="C169" t="n">
-        <v>-0</v>
+        <v>10000</v>
       </c>
       <c r="D169" t="n">
         <v>2667.698142161701</v>
@@ -22943,7 +22943,7 @@
         <v>5000000</v>
       </c>
       <c r="D2" t="n">
-        <v>2739.130434782609</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="3">
@@ -22957,7 +22957,7 @@
         <v>5000000</v>
       </c>
       <c r="D3" t="n">
-        <v>1579.481246623229</v>
+        <v>2739.130434782609</v>
       </c>
     </row>
     <row r="4">
@@ -22971,7 +22971,7 @@
         <v>5000000</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>340.8855480808256</v>
       </c>
     </row>
     <row r="5">
@@ -22985,7 +22985,7 @@
         <v>5000000</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>340.8855480808256</v>
       </c>
     </row>
     <row r="6">
@@ -22999,7 +22999,7 @@
         <v>5000000</v>
       </c>
       <c r="D6" t="n">
-        <v>592.0739632459071</v>
+        <v>932.9595113267327</v>
       </c>
     </row>
     <row r="7">
@@ -23013,7 +23013,7 @@
         <v>5000000</v>
       </c>
       <c r="D7" t="n">
-        <v>1100.18510936148</v>
+        <v>1441.070657442305</v>
       </c>
     </row>
     <row r="8">
@@ -23024,10 +23024,10 @@
         <v>53397.04</v>
       </c>
       <c r="C8" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D8" t="n">
-        <v>752.5530949263552</v>
+        <v>1093.438643007181</v>
       </c>
     </row>
     <row r="9">
@@ -23038,7 +23038,7 @@
         <v>53397.04</v>
       </c>
       <c r="C9" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D9" t="n">
         <v>-0</v>
@@ -23052,7 +23052,7 @@
         <v>53397.04</v>
       </c>
       <c r="C10" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D10" t="n">
         <v>-0</v>
@@ -23066,7 +23066,7 @@
         <v>53397.04</v>
       </c>
       <c r="C11" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D11" t="n">
         <v>-0</v>
@@ -23080,7 +23080,7 @@
         <v>53397.04</v>
       </c>
       <c r="C12" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D12" t="n">
         <v>-0</v>
@@ -23094,7 +23094,7 @@
         <v>53397.04</v>
       </c>
       <c r="C13" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D13" t="n">
         <v>960</v>
@@ -23108,7 +23108,7 @@
         <v>53397.04</v>
       </c>
       <c r="C14" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D14" t="n">
         <v>3720</v>
@@ -23122,7 +23122,7 @@
         <v>53397.04</v>
       </c>
       <c r="C15" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D15" t="n">
         <v>6480</v>
@@ -23136,7 +23136,7 @@
         <v>53397.04</v>
       </c>
       <c r="C16" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D16" t="n">
         <v>9240</v>
@@ -23150,7 +23150,7 @@
         <v>53397.04</v>
       </c>
       <c r="C17" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D17" t="n">
         <v>12000</v>
@@ -23164,7 +23164,7 @@
         <v>53397.04</v>
       </c>
       <c r="C18" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D18" t="n">
         <v>12000</v>
@@ -23178,10 +23178,10 @@
         <v>53397.04</v>
       </c>
       <c r="C19" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D19" t="n">
-        <v>8739.130434782608</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="20">
@@ -23192,10 +23192,10 @@
         <v>53397.04</v>
       </c>
       <c r="C20" t="n">
-        <v>5006521.195282</v>
+        <v>5000000</v>
       </c>
       <c r="D20" t="n">
-        <v>8739.130434782608</v>
+        <v>9782.608695652172</v>
       </c>
     </row>
     <row r="21">
@@ -23206,10 +23206,10 @@
         <v>53397.04</v>
       </c>
       <c r="C21" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D21" t="n">
-        <v>8739.130434782608</v>
+        <v>6521.739130434782</v>
       </c>
     </row>
     <row r="22">
@@ -23220,10 +23220,10 @@
         <v>53397.04</v>
       </c>
       <c r="C22" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D22" t="n">
-        <v>6250.242120259173</v>
+        <v>3260.869565217391</v>
       </c>
     </row>
     <row r="23">
@@ -23234,10 +23234,10 @@
         <v>53397.04</v>
       </c>
       <c r="C23" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D23" t="n">
-        <v>6250.242120259173</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -23248,10 +23248,10 @@
         <v>53397.04</v>
       </c>
       <c r="C24" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D24" t="n">
-        <v>2989.372555041782</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -23262,7 +23262,7 @@
         <v>53397.04</v>
       </c>
       <c r="C25" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D25" t="n">
         <v>-0</v>
@@ -23276,7 +23276,7 @@
         <v>53397.04</v>
       </c>
       <c r="C26" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D26" t="n">
         <v>-0</v>
@@ -23290,7 +23290,7 @@
         <v>53397.04</v>
       </c>
       <c r="C27" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D27" t="n">
         <v>-0</v>
@@ -23304,10 +23304,10 @@
         <v>53397.04</v>
       </c>
       <c r="C28" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D28" t="n">
-        <v>283.3214320014952</v>
+        <v>848.1600952681014</v>
       </c>
     </row>
     <row r="29">
@@ -23318,10 +23318,10 @@
         <v>53397.04</v>
       </c>
       <c r="C29" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D29" t="n">
-        <v>2013.600845938875</v>
+        <v>2049.856228957269</v>
       </c>
     </row>
     <row r="30">
@@ -23332,10 +23332,10 @@
         <v>53397.04</v>
       </c>
       <c r="C30" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D30" t="n">
-        <v>3837.120706498562</v>
+        <v>4809.856228957269</v>
       </c>
     </row>
     <row r="31">
@@ -23346,7 +23346,7 @@
         <v>53397.04</v>
       </c>
       <c r="C31" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D31" t="n">
         <v>4809.856228957269</v>
@@ -23360,7 +23360,7 @@
         <v>53397.04</v>
       </c>
       <c r="C32" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D32" t="n">
         <v>3260.869565217391</v>
@@ -23374,7 +23374,7 @@
         <v>53397.04</v>
       </c>
       <c r="C33" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D33" t="n">
         <v>-0</v>
@@ -23388,7 +23388,7 @@
         <v>53397.04</v>
       </c>
       <c r="C34" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D34" t="n">
         <v>-0</v>
@@ -23402,7 +23402,7 @@
         <v>53397.04</v>
       </c>
       <c r="C35" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D35" t="n">
         <v>-0</v>
@@ -23416,7 +23416,7 @@
         <v>53397.04</v>
       </c>
       <c r="C36" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D36" t="n">
         <v>-0</v>
@@ -23430,7 +23430,7 @@
         <v>53397.04</v>
       </c>
       <c r="C37" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D37" t="n">
         <v>960</v>
@@ -23444,7 +23444,7 @@
         <v>53397.04</v>
       </c>
       <c r="C38" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D38" t="n">
         <v>3720</v>
@@ -23458,7 +23458,7 @@
         <v>53397.04</v>
       </c>
       <c r="C39" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D39" t="n">
         <v>6480</v>
@@ -23472,7 +23472,7 @@
         <v>53397.04</v>
       </c>
       <c r="C40" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D40" t="n">
         <v>9240</v>
@@ -23486,7 +23486,7 @@
         <v>53397.04</v>
       </c>
       <c r="C41" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D41" t="n">
         <v>12000</v>
@@ -23500,10 +23500,10 @@
         <v>53397.04</v>
       </c>
       <c r="C42" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D42" t="n">
-        <v>10245.12324553768</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="43">
@@ -23514,10 +23514,10 @@
         <v>53397.04</v>
       </c>
       <c r="C43" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D43" t="n">
-        <v>6984.253680320291</v>
+        <v>8739.130434782608</v>
       </c>
     </row>
     <row r="44">
@@ -23528,10 +23528,10 @@
         <v>53397.04</v>
       </c>
       <c r="C44" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D44" t="n">
-        <v>3765.132519919986</v>
+        <v>5478.260869565217</v>
       </c>
     </row>
     <row r="45">
@@ -23542,10 +23542,10 @@
         <v>53397.04</v>
       </c>
       <c r="C45" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D45" t="n">
-        <v>2875.594283730519</v>
+        <v>2217.391304347826</v>
       </c>
     </row>
     <row r="46">
@@ -23556,10 +23556,10 @@
         <v>53397.04</v>
       </c>
       <c r="C46" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D46" t="n">
-        <v>2875.594283730519</v>
+        <v>2183.622978670569</v>
       </c>
     </row>
     <row r="47">
@@ -23570,7 +23570,7 @@
         <v>53397.04</v>
       </c>
       <c r="C47" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D47" t="n">
         <v>-0</v>
@@ -23584,7 +23584,7 @@
         <v>53397.04</v>
       </c>
       <c r="C48" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D48" t="n">
         <v>-0</v>
@@ -23598,7 +23598,7 @@
         <v>53397.04</v>
       </c>
       <c r="C49" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D49" t="n">
         <v>-0</v>
@@ -23612,7 +23612,7 @@
         <v>53397.04</v>
       </c>
       <c r="C50" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D50" t="n">
         <v>-0</v>
@@ -23626,7 +23626,7 @@
         <v>53397.04</v>
       </c>
       <c r="C51" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D51" t="n">
         <v>-0</v>
@@ -23640,7 +23640,7 @@
         <v>53397.04</v>
       </c>
       <c r="C52" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D52" t="n">
         <v>-0</v>
@@ -23654,7 +23654,7 @@
         <v>53397.04</v>
       </c>
       <c r="C53" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D53" t="n">
         <v>-0</v>
@@ -23668,7 +23668,7 @@
         <v>53397.04</v>
       </c>
       <c r="C54" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D54" t="n">
         <v>-0</v>
@@ -23682,7 +23682,7 @@
         <v>53397.04</v>
       </c>
       <c r="C55" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D55" t="n">
         <v>1876.751066427707</v>
@@ -23696,7 +23696,7 @@
         <v>53397.04</v>
       </c>
       <c r="C56" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D56" t="n">
         <v>3521.915390091896</v>
@@ -23710,7 +23710,7 @@
         <v>53397.04</v>
       </c>
       <c r="C57" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D57" t="n">
         <v>2208.128748191953</v>
@@ -23724,7 +23724,7 @@
         <v>53397.04</v>
       </c>
       <c r="C58" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D58" t="n">
         <v>-0</v>
@@ -23738,7 +23738,7 @@
         <v>53397.04</v>
       </c>
       <c r="C59" t="n">
-        <v>5011775.541319128</v>
+        <v>5000000</v>
       </c>
       <c r="D59" t="n">
         <v>-0</v>
@@ -23752,10 +23752,10 @@
         <v>53397.04</v>
       </c>
       <c r="C60" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D60" t="n">
-        <v>960</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="61">
@@ -23766,7 +23766,7 @@
         <v>53397.04</v>
       </c>
       <c r="C61" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D61" t="n">
         <v>960</v>
@@ -23780,7 +23780,7 @@
         <v>53397.04</v>
       </c>
       <c r="C62" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D62" t="n">
         <v>3720</v>
@@ -23794,7 +23794,7 @@
         <v>53397.04</v>
       </c>
       <c r="C63" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D63" t="n">
         <v>6480</v>
@@ -23808,7 +23808,7 @@
         <v>53397.04</v>
       </c>
       <c r="C64" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D64" t="n">
         <v>9240</v>
@@ -23822,7 +23822,7 @@
         <v>53397.04</v>
       </c>
       <c r="C65" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D65" t="n">
         <v>12000</v>
@@ -23836,7 +23836,7 @@
         <v>40875.5225109482</v>
       </c>
       <c r="C66" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D66" t="n">
         <v>11533.8380721424</v>
@@ -23850,7 +23850,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C67" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D67" t="n">
         <v>8272.968506925008</v>
@@ -23864,10 +23864,10 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C68" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D68" t="n">
-        <v>5012.098941707617</v>
+        <v>5434.173506234933</v>
       </c>
     </row>
     <row r="69">
@@ -23878,7 +23878,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C69" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D69" t="n">
         <v>3260.869565217391</v>
@@ -23892,7 +23892,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C70" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D70" t="n">
         <v>-0</v>
@@ -23906,7 +23906,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C71" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D71" t="n">
         <v>-0</v>
@@ -23920,7 +23920,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C72" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D72" t="n">
         <v>-0</v>
@@ -23934,7 +23934,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C73" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D73" t="n">
         <v>-0</v>
@@ -23948,7 +23948,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C74" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D74" t="n">
         <v>-0</v>
@@ -23962,7 +23962,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C75" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D75" t="n">
         <v>-0</v>
@@ -23976,7 +23976,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C76" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D76" t="n">
         <v>-0</v>
@@ -23990,7 +23990,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C77" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D77" t="n">
         <v>-0</v>
@@ -24004,7 +24004,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C78" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D78" t="n">
         <v>236.8206695802409</v>
@@ -24018,7 +24018,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C79" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D79" t="n">
         <v>878.555123518212</v>
@@ -24032,7 +24032,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C80" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D80" t="n">
         <v>924.0487091321143</v>
@@ -24046,10 +24046,10 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C81" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D81" t="n">
-        <v>924.0487091321143</v>
+        <v>88.81597663246339</v>
       </c>
     </row>
     <row r="82">
@@ -24060,10 +24060,10 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C82" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D82" t="n">
-        <v>924.0487091321143</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="83">
@@ -24074,7 +24074,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C83" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D83" t="n">
         <v>-0</v>
@@ -24088,7 +24088,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C84" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D84" t="n">
         <v>960</v>
@@ -24102,7 +24102,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C85" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D85" t="n">
         <v>3720</v>
@@ -24116,7 +24116,7 @@
         <v>24259.85924782163</v>
       </c>
       <c r="C86" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D86" t="n">
         <v>6480</v>
@@ -24130,7 +24130,7 @@
         <v>45940.27836459656</v>
       </c>
       <c r="C87" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D87" t="n">
         <v>9240</v>
@@ -24144,7 +24144,7 @@
         <v>69877.69250524332</v>
       </c>
       <c r="C88" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D88" t="n">
         <v>12000</v>
@@ -24158,7 +24158,7 @@
         <v>93815.10664589008</v>
       </c>
       <c r="C89" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D89" t="n">
         <v>12000</v>
@@ -24172,7 +24172,7 @@
         <v>106794.08</v>
       </c>
       <c r="C90" t="n">
-        <v>5016445.637227128</v>
+        <v>5000000</v>
       </c>
       <c r="D90" t="n">
         <v>9206.453562208684</v>
@@ -24186,7 +24186,7 @@
         <v>77015.96921484145</v>
       </c>
       <c r="C91" t="n">
-        <v>5008108.407023179</v>
+        <v>4991662.769796051</v>
       </c>
       <c r="D91" t="n">
         <v>5945.583996991293</v>
@@ -24200,7 +24200,7 @@
         <v>47237.85842968289</v>
       </c>
       <c r="C92" t="n">
-        <v>4999653.88758923</v>
+        <v>4983208.250362102</v>
       </c>
       <c r="D92" t="n">
         <v>2684.714431773902</v>
@@ -24214,10 +24214,10 @@
         <v>17459.74764452434</v>
       </c>
       <c r="C93" t="n">
-        <v>4993301.689286176</v>
+        <v>4976856.052059048</v>
       </c>
       <c r="D93" t="n">
-        <v>-0</v>
+        <v>1394.281998768597</v>
       </c>
     </row>
     <row r="94">
@@ -24228,10 +24228,10 @@
         <v>-0</v>
       </c>
       <c r="C94" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D94" t="n">
-        <v>-0</v>
+        <v>1394.281998768597</v>
       </c>
     </row>
     <row r="95">
@@ -24242,10 +24242,10 @@
         <v>-0</v>
       </c>
       <c r="C95" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D95" t="n">
-        <v>-0</v>
+        <v>1394.281998768597</v>
       </c>
     </row>
     <row r="96">
@@ -24256,7 +24256,7 @@
         <v>-0</v>
       </c>
       <c r="C96" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D96" t="n">
         <v>-0</v>
@@ -24270,7 +24270,7 @@
         <v>-0</v>
       </c>
       <c r="C97" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D97" t="n">
         <v>-0</v>
@@ -24284,7 +24284,7 @@
         <v>-0</v>
       </c>
       <c r="C98" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D98" t="n">
         <v>-0</v>
@@ -24298,7 +24298,7 @@
         <v>-0</v>
       </c>
       <c r="C99" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D99" t="n">
         <v>-0</v>
@@ -24312,7 +24312,7 @@
         <v>-0</v>
       </c>
       <c r="C100" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D100" t="n">
         <v>-0</v>
@@ -24326,7 +24326,7 @@
         <v>-0</v>
       </c>
       <c r="C101" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D101" t="n">
         <v>-0</v>
@@ -24340,7 +24340,7 @@
         <v>-0</v>
       </c>
       <c r="C102" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D102" t="n">
         <v>-0</v>
@@ -24354,7 +24354,7 @@
         <v>-0</v>
       </c>
       <c r="C103" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D103" t="n">
         <v>-0</v>
@@ -24368,7 +24368,7 @@
         <v>-0</v>
       </c>
       <c r="C104" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D104" t="n">
         <v>9.861112481922131</v>
@@ -24382,7 +24382,7 @@
         <v>-0</v>
       </c>
       <c r="C105" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D105" t="n">
         <v>-0</v>
@@ -24396,7 +24396,7 @@
         <v>-0</v>
       </c>
       <c r="C106" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D106" t="n">
         <v>-0</v>
@@ -24410,7 +24410,7 @@
         <v>-0</v>
       </c>
       <c r="C107" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D107" t="n">
         <v>-0</v>
@@ -24424,10 +24424,10 @@
         <v>-0</v>
       </c>
       <c r="C108" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D108" t="n">
-        <v>-0</v>
+        <v>960</v>
       </c>
     </row>
     <row r="109">
@@ -24438,7 +24438,7 @@
         <v>-0</v>
       </c>
       <c r="C109" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D109" t="n">
         <v>960</v>
@@ -24452,7 +24452,7 @@
         <v>-0</v>
       </c>
       <c r="C110" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D110" t="n">
         <v>3720</v>
@@ -24466,7 +24466,7 @@
         <v>-0</v>
       </c>
       <c r="C111" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D111" t="n">
         <v>6480</v>
@@ -24480,7 +24480,7 @@
         <v>-0</v>
       </c>
       <c r="C112" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D112" t="n">
         <v>9240</v>
@@ -24494,7 +24494,7 @@
         <v>-0</v>
       </c>
       <c r="C113" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D113" t="n">
         <v>12000</v>
@@ -24508,7 +24508,7 @@
         <v>-0</v>
       </c>
       <c r="C114" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D114" t="n">
         <v>12000</v>
@@ -24522,7 +24522,7 @@
         <v>-0</v>
       </c>
       <c r="C115" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D115" t="n">
         <v>8739.130434782608</v>
@@ -24536,10 +24536,10 @@
         <v>-0</v>
       </c>
       <c r="C116" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D116" t="n">
-        <v>6521.739130434782</v>
+        <v>5478.260869565217</v>
       </c>
     </row>
     <row r="117">
@@ -24550,10 +24550,10 @@
         <v>-0</v>
       </c>
       <c r="C117" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D117" t="n">
-        <v>3260.869565217391</v>
+        <v>3439.18639934254</v>
       </c>
     </row>
     <row r="118">
@@ -24564,10 +24564,10 @@
         <v>-0</v>
       </c>
       <c r="C118" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D118" t="n">
-        <v>-0</v>
+        <v>178.3168341251486</v>
       </c>
     </row>
     <row r="119">
@@ -24578,7 +24578,7 @@
         <v>-0</v>
       </c>
       <c r="C119" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D119" t="n">
         <v>-0</v>
@@ -24592,7 +24592,7 @@
         <v>-0</v>
       </c>
       <c r="C120" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D120" t="n">
         <v>-0</v>
@@ -24606,7 +24606,7 @@
         <v>-0</v>
       </c>
       <c r="C121" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D121" t="n">
         <v>-0</v>
@@ -24620,7 +24620,7 @@
         <v>-0</v>
       </c>
       <c r="C122" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D122" t="n">
         <v>-0</v>
@@ -24634,10 +24634,10 @@
         <v>-0</v>
       </c>
       <c r="C123" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D123" t="n">
-        <v>2217.717998303116</v>
+        <v>171.7442958679827</v>
       </c>
     </row>
     <row r="124">
@@ -24648,10 +24648,10 @@
         <v>-0</v>
       </c>
       <c r="C124" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D124" t="n">
-        <v>2673.070284033752</v>
+        <v>627.096581598619</v>
       </c>
     </row>
     <row r="125">
@@ -24662,10 +24662,10 @@
         <v>-0</v>
       </c>
       <c r="C125" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D125" t="n">
-        <v>3124.750937983564</v>
+        <v>1078.777235548431</v>
       </c>
     </row>
     <row r="126">
@@ -24676,10 +24676,10 @@
         <v>-0</v>
       </c>
       <c r="C126" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D126" t="n">
-        <v>3124.750937983564</v>
+        <v>1078.777235548431</v>
       </c>
     </row>
     <row r="127">
@@ -24690,7 +24690,7 @@
         <v>-0</v>
       </c>
       <c r="C127" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D127" t="n">
         <v>3124.750937983564</v>
@@ -24704,7 +24704,7 @@
         <v>-0</v>
       </c>
       <c r="C128" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D128" t="n">
         <v>3124.750937983564</v>
@@ -24718,7 +24718,7 @@
         <v>-0</v>
       </c>
       <c r="C129" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D129" t="n">
         <v>-0</v>
@@ -24732,7 +24732,7 @@
         <v>-0</v>
       </c>
       <c r="C130" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D130" t="n">
         <v>-0</v>
@@ -24746,7 +24746,7 @@
         <v>-0</v>
       </c>
       <c r="C131" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D131" t="n">
         <v>-0</v>
@@ -24760,10 +24760,10 @@
         <v>-0</v>
       </c>
       <c r="C132" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D132" t="n">
-        <v>960</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="133">
@@ -24774,7 +24774,7 @@
         <v>-0</v>
       </c>
       <c r="C133" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D133" t="n">
         <v>960</v>
@@ -24788,7 +24788,7 @@
         <v>-0</v>
       </c>
       <c r="C134" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D134" t="n">
         <v>3720</v>
@@ -24802,7 +24802,7 @@
         <v>-0</v>
       </c>
       <c r="C135" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D135" t="n">
         <v>6480</v>
@@ -24816,7 +24816,7 @@
         <v>-0</v>
       </c>
       <c r="C136" t="n">
-        <v>4987697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D136" t="n">
         <v>9240</v>
@@ -24830,7 +24830,7 @@
         <v>-0</v>
       </c>
       <c r="C137" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D137" t="n">
         <v>12000</v>
@@ -24844,10 +24844,10 @@
         <v>-0</v>
       </c>
       <c r="C138" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D138" t="n">
-        <v>12000</v>
+        <v>9782.608695652172</v>
       </c>
     </row>
     <row r="139">
@@ -24858,10 +24858,10 @@
         <v>-0</v>
       </c>
       <c r="C139" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D139" t="n">
-        <v>8739.130434782608</v>
+        <v>6521.739130434782</v>
       </c>
     </row>
     <row r="140">
@@ -24872,10 +24872,10 @@
         <v>-0</v>
       </c>
       <c r="C140" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D140" t="n">
-        <v>5478.260869565217</v>
+        <v>3260.869565217391</v>
       </c>
     </row>
     <row r="141">
@@ -24886,10 +24886,10 @@
         <v>-0</v>
       </c>
       <c r="C141" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D141" t="n">
-        <v>2217.391304347826</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="142">
@@ -24900,7 +24900,7 @@
         <v>-0</v>
       </c>
       <c r="C142" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D142" t="n">
         <v>-0</v>
@@ -24914,7 +24914,7 @@
         <v>-0</v>
       </c>
       <c r="C143" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D143" t="n">
         <v>-0</v>
@@ -24928,7 +24928,7 @@
         <v>-0</v>
       </c>
       <c r="C144" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D144" t="n">
         <v>1144.085240486018</v>
@@ -24942,7 +24942,7 @@
         <v>-0</v>
       </c>
       <c r="C145" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D145" t="n">
         <v>2813.80776898769</v>
@@ -24956,7 +24956,7 @@
         <v>-0</v>
       </c>
       <c r="C146" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D146" t="n">
         <v>4214.387362351576</v>
@@ -24970,7 +24970,7 @@
         <v>-0</v>
       </c>
       <c r="C147" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D147" t="n">
         <v>4759.890047191001</v>
@@ -24984,10 +24984,10 @@
         <v>-0</v>
       </c>
       <c r="C148" t="n">
-        <v>4997697.997990889</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D148" t="n">
-        <v>4759.890047191001</v>
+        <v>3601.192146157744</v>
       </c>
     </row>
     <row r="149">
@@ -24998,10 +24998,10 @@
         <v>-0</v>
       </c>
       <c r="C149" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D149" t="n">
-        <v>4759.890047191001</v>
+        <v>3601.192146157744</v>
       </c>
     </row>
     <row r="150">
@@ -25012,10 +25012,10 @@
         <v>-0</v>
       </c>
       <c r="C150" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D150" t="n">
-        <v>3274.357605364062</v>
+        <v>3601.192146157744</v>
       </c>
     </row>
     <row r="151">
@@ -25026,10 +25026,10 @@
         <v>-0</v>
       </c>
       <c r="C151" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D151" t="n">
-        <v>3274.357605364062</v>
+        <v>3601.192146157744</v>
       </c>
     </row>
     <row r="152">
@@ -25040,10 +25040,10 @@
         <v>-0</v>
       </c>
       <c r="C152" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D152" t="n">
-        <v>13.48804014667068</v>
+        <v>3260.869565217391</v>
       </c>
     </row>
     <row r="153">
@@ -25054,7 +25054,7 @@
         <v>-0</v>
       </c>
       <c r="C153" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D153" t="n">
         <v>-0</v>
@@ -25068,7 +25068,7 @@
         <v>-0</v>
       </c>
       <c r="C154" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D154" t="n">
         <v>-0</v>
@@ -25082,7 +25082,7 @@
         <v>-0</v>
       </c>
       <c r="C155" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D155" t="n">
         <v>-0</v>
@@ -25096,7 +25096,7 @@
         <v>-0</v>
       </c>
       <c r="C156" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D156" t="n">
         <v>-0</v>
@@ -25110,7 +25110,7 @@
         <v>-0</v>
       </c>
       <c r="C157" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D157" t="n">
         <v>960</v>
@@ -25124,7 +25124,7 @@
         <v>-0</v>
       </c>
       <c r="C158" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D158" t="n">
         <v>3720</v>
@@ -25138,7 +25138,7 @@
         <v>-0</v>
       </c>
       <c r="C159" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D159" t="n">
         <v>6480</v>
@@ -25152,7 +25152,7 @@
         <v>-0</v>
       </c>
       <c r="C160" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D160" t="n">
         <v>9240</v>
@@ -25166,7 +25166,7 @@
         <v>-0</v>
       </c>
       <c r="C161" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D161" t="n">
         <v>12000</v>
@@ -25180,7 +25180,7 @@
         <v>-0</v>
       </c>
       <c r="C162" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D162" t="n">
         <v>12000</v>
@@ -25194,7 +25194,7 @@
         <v>-0</v>
       </c>
       <c r="C163" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D163" t="n">
         <v>8739.130434782608</v>
@@ -25208,7 +25208,7 @@
         <v>-0</v>
       </c>
       <c r="C164" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D164" t="n">
         <v>5478.260869565217</v>
@@ -25222,7 +25222,7 @@
         <v>-0</v>
       </c>
       <c r="C165" t="n">
-        <v>5000000</v>
+        <v>4971252.360763761</v>
       </c>
       <c r="D165" t="n">
         <v>2217.391304347826</v>
@@ -25236,7 +25236,7 @@
         <v>-0</v>
       </c>
       <c r="C166" t="n">
-        <v>5000000</v>
+        <v>4973559.906262</v>
       </c>
       <c r="D166" t="n">
         <v>1902.438437348435</v>
@@ -25250,7 +25250,7 @@
         <v>5522.21171870648</v>
       </c>
       <c r="C167" t="n">
-        <v>5000000</v>
+        <v>4981737.50715</v>
       </c>
       <c r="D167" t="n">
         <v>2384.436424058699</v>
@@ -25264,7 +25264,7 @@
         <v>29459.62585935324</v>
       </c>
       <c r="C168" t="n">
-        <v>5000000</v>
+        <v>4990000</v>
       </c>
       <c r="D168" t="n">
         <v>3545.717709211235</v>
@@ -25373,7 +25373,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -25382,7 +25382,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -25405,7 +25405,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -25428,7 +25428,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -25451,7 +25451,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -25810,10 +25810,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-3.637978807091713e-12</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -25911,7 +25911,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -25980,7 +25980,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -26003,7 +26003,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -26026,7 +26026,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -26049,7 +26049,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -26302,7 +26302,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -26348,7 +26348,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -26394,7 +26394,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -26440,7 +26440,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -26713,10 +26713,10 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="F60" t="n">
         <v>2.273736754432321e-13</v>
@@ -26739,7 +26739,7 @@
         <v>1.818989403545856e-12</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>2.273736754432321e-13</v>
@@ -27015,7 +27015,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -27199,7 +27199,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -27245,7 +27245,7 @@
         <v>1.818989403545856e-12</v>
       </c>
       <c r="E83" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -27590,7 +27590,7 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>1.364242052659392e-12</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -27820,7 +27820,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -27843,7 +27843,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -28027,7 +28027,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>-1.818989403545856e-12</v>
+        <v>-2.728484105318785e-12</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -28073,7 +28073,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -28142,7 +28142,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>1.364242052659392e-12</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -28372,7 +28372,7 @@
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>-9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -28395,7 +28395,7 @@
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -28786,7 +28786,7 @@
         <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -29148,7 +29148,7 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -29168,7 +29168,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -29191,7 +29191,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>-5.456968210637569e-12</v>
+        <v>-3.637978807091713e-12</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -29214,16 +29214,16 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
+        <v>1.091393642127514e-11</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
         <v>1.818989403545856e-12</v>
-      </c>
-      <c r="C169" t="n">
-        <v>0</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" t="n">
-        <v>0</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -29305,16 +29305,16 @@
         <v>0.01</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>89.41176470588235</v>
       </c>
       <c r="G2" t="n">
         <v>72</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>102.5787545787546</v>
       </c>
       <c r="I2" t="n">
-        <v>14</v>
+        <v>89.41176470588235</v>
       </c>
     </row>
     <row r="3">
@@ -31161,7 +31161,7 @@
         <v>0.1124399864622779</v>
       </c>
       <c r="F66" t="n">
-        <v>89.41176470588233</v>
+        <v>89.41176470588235</v>
       </c>
       <c r="G66" t="n">
         <v>72</v>
@@ -31170,7 +31170,7 @@
         <v>102.7288497970143</v>
       </c>
       <c r="I66" t="n">
-        <v>89.41176470588233</v>
+        <v>89.41176470588235</v>
       </c>
     </row>
     <row r="67">
@@ -31944,7 +31944,7 @@
         <v>1.41</v>
       </c>
       <c r="F93" t="n">
-        <v>89.41176470588235</v>
+        <v>89.41176470588233</v>
       </c>
       <c r="G93" t="n">
         <v>72</v>
@@ -31953,7 +31953,7 @@
         <v>104.6300366300366</v>
       </c>
       <c r="I93" t="n">
-        <v>89.41176470588235</v>
+        <v>89.41176470588233</v>
       </c>
     </row>
     <row r="94">
@@ -33423,7 +33423,7 @@
         <v>0.01</v>
       </c>
       <c r="F144" t="n">
-        <v>75.59347764705882</v>
+        <v>75.59347764705883</v>
       </c>
       <c r="G144" t="n">
         <v>72</v>
@@ -33432,7 +33432,7 @@
         <v>102.5787545787546</v>
       </c>
       <c r="I144" t="n">
-        <v>75.59347764705882</v>
+        <v>75.59347764705883</v>
       </c>
     </row>
     <row r="145">
@@ -33452,7 +33452,7 @@
         <v>0.01</v>
       </c>
       <c r="F145" t="n">
-        <v>75.59347764705882</v>
+        <v>75.59347764705883</v>
       </c>
       <c r="G145" t="n">
         <v>72</v>
@@ -33461,7 +33461,7 @@
         <v>102.5787545787546</v>
       </c>
       <c r="I145" t="n">
-        <v>75.59347764705882</v>
+        <v>75.59347764705883</v>
       </c>
     </row>
     <row r="146">
@@ -33481,7 +33481,7 @@
         <v>0.01</v>
       </c>
       <c r="F146" t="n">
-        <v>75.59347764705882</v>
+        <v>75.59347764705883</v>
       </c>
       <c r="G146" t="n">
         <v>72</v>
@@ -33490,7 +33490,7 @@
         <v>102.5787545787546</v>
       </c>
       <c r="I146" t="n">
-        <v>75.59347764705882</v>
+        <v>75.59347764705883</v>
       </c>
     </row>
     <row r="147">
@@ -33510,7 +33510,7 @@
         <v>0.01</v>
       </c>
       <c r="F147" t="n">
-        <v>75.59347764705882</v>
+        <v>75.59347764705883</v>
       </c>
       <c r="G147" t="n">
         <v>72</v>
@@ -33519,7 +33519,7 @@
         <v>102.5787545787546</v>
       </c>
       <c r="I147" t="n">
-        <v>75.59347764705882</v>
+        <v>75.59347764705883</v>
       </c>
     </row>
     <row r="148">
@@ -33684,7 +33684,7 @@
         <v>0.01</v>
       </c>
       <c r="F153" t="n">
-        <v>89.41176470588233</v>
+        <v>89.41176470588235</v>
       </c>
       <c r="G153" t="n">
         <v>72</v>
@@ -33693,7 +33693,7 @@
         <v>102.5787545787546</v>
       </c>
       <c r="I153" t="n">
-        <v>89.41176470588233</v>
+        <v>89.41176470588235</v>
       </c>
     </row>
     <row r="154">
@@ -37146,7 +37146,7 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>27352.18472970763</v>
+        <v>27352.18575534866</v>
       </c>
       <c r="D2" t="n">
         <v>-0</v>
@@ -37167,7 +37167,7 @@
         <v>14283.4968</v>
       </c>
       <c r="J2" t="n">
-        <v>1228.171318466184</v>
+        <v>1607</v>
       </c>
       <c r="K2" t="n">
         <v>-0</v>
@@ -37214,7 +37214,7 @@
         <v>15974.0556</v>
       </c>
       <c r="J3" t="n">
-        <v>250.3169522480473</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
@@ -37308,7 +37308,7 @@
         <v>17975.1252</v>
       </c>
       <c r="J5" t="n">
-        <v>278.5065309906845</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
         <v>-0</v>
@@ -37428,7 +37428,7 @@
         <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>29438.92075836087</v>
+        <v>20122.92749836087</v>
       </c>
       <c r="D8" t="n">
         <v>-0</v>
@@ -37981,7 +37981,7 @@
         <v>486.178</v>
       </c>
       <c r="O19" t="n">
-        <v>5236.421781558203</v>
+        <v>8236.421781558203</v>
       </c>
     </row>
     <row r="20">
@@ -38028,7 +38028,7 @@
         <v>317.504</v>
       </c>
       <c r="O20" t="n">
-        <v>11342.96253380869</v>
+        <v>9302.96253380869</v>
       </c>
     </row>
     <row r="21">
@@ -38039,7 +38039,7 @@
         <v>-0</v>
       </c>
       <c r="C21" t="n">
-        <v>47588.02025135333</v>
+        <v>40081.81162688446</v>
       </c>
       <c r="D21" t="n">
         <v>-0</v>
@@ -38075,7 +38075,7 @@
         <v>257.972</v>
       </c>
       <c r="O21" t="n">
-        <v>12604.44566335859</v>
+        <v>9604.445663358589</v>
       </c>
     </row>
     <row r="22">
@@ -38122,7 +38122,7 @@
         <v>307.582</v>
       </c>
       <c r="O22" t="n">
-        <v>10326.57493845887</v>
+        <v>9616.352187820432</v>
       </c>
     </row>
     <row r="23">
@@ -38169,7 +38169,7 @@
         <v>486.178</v>
       </c>
       <c r="O23" t="n">
-        <v>11055.08244692024</v>
+        <v>8055.082446920236</v>
       </c>
     </row>
     <row r="24">
@@ -38216,7 +38216,7 @@
         <v>912.824</v>
       </c>
       <c r="O24" t="n">
-        <v>4800.621257879136</v>
+        <v>7800.621257879136</v>
       </c>
     </row>
     <row r="25">
@@ -38263,7 +38263,7 @@
         <v>1617.286</v>
       </c>
       <c r="O25" t="n">
-        <v>-0</v>
+        <v>2750.222750638439</v>
       </c>
     </row>
     <row r="26">
@@ -38389,7 +38389,7 @@
         <v>14145.492</v>
       </c>
       <c r="J28" t="n">
-        <v>993.0449312319499</v>
+        <v>1607</v>
       </c>
       <c r="K28" t="n">
         <v>-0</v>
@@ -38436,7 +38436,7 @@
         <v>14490.504</v>
       </c>
       <c r="J29" t="n">
-        <v>1607</v>
+        <v>1032.452956251943</v>
       </c>
       <c r="K29" t="n">
         <v>-0</v>
@@ -38483,7 +38483,7 @@
         <v>15732.5472</v>
       </c>
       <c r="J30" t="n">
-        <v>-0</v>
+        <v>1017.913195043818</v>
       </c>
       <c r="K30" t="n">
         <v>-0</v>
@@ -38530,7 +38530,7 @@
         <v>15491.0388</v>
       </c>
       <c r="J31" t="n">
-        <v>-0</v>
+        <v>1607</v>
       </c>
       <c r="K31" t="n">
         <v>-0</v>
@@ -39047,7 +39047,7 @@
         <v>12558.4368</v>
       </c>
       <c r="J42" t="n">
-        <v>1607</v>
+        <v>-0</v>
       </c>
       <c r="K42" t="n">
         <v>-0</v>
@@ -39141,7 +39141,7 @@
         <v>23184.8064</v>
       </c>
       <c r="J44" t="n">
-        <v>1607</v>
+        <v>1568.591467568281</v>
       </c>
       <c r="K44" t="n">
         <v>-0</v>
@@ -39188,7 +39188,7 @@
         <v>26807.4324</v>
       </c>
       <c r="J45" t="n">
-        <v>-0</v>
+        <v>1607</v>
       </c>
       <c r="K45" t="n">
         <v>-0</v>
@@ -39235,7 +39235,7 @@
         <v>27014.4396</v>
       </c>
       <c r="J46" t="n">
-        <v>31.06685962307637</v>
+        <v>-0</v>
       </c>
       <c r="K46" t="n">
         <v>-0</v>
@@ -39329,7 +39329,7 @@
         <v>25875.9</v>
       </c>
       <c r="J48" t="n">
-        <v>882.4634322258155</v>
+        <v>-0</v>
       </c>
       <c r="K48" t="n">
         <v>-0</v>
@@ -39869,7 +39869,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>49321.40961329302</v>
+        <v>42649.84403043588</v>
       </c>
       <c r="C60" t="n">
         <v>-0</v>
@@ -39887,7 +39887,7 @@
         <v>4559.973599999999</v>
       </c>
       <c r="H60" t="n">
-        <v>8629.818497660173</v>
+        <v>7586.340236790606</v>
       </c>
       <c r="I60" t="n">
         <v>15698.046</v>
@@ -39934,7 +39934,7 @@
         <v>2849.9835</v>
       </c>
       <c r="H61" t="n">
-        <v>22573.37954696673</v>
+        <v>23616.8578078363</v>
       </c>
       <c r="I61" t="n">
         <v>-0</v>
@@ -40504,7 +40504,7 @@
         <v>20873.226</v>
       </c>
       <c r="J73" t="n">
-        <v>37.12940599690462</v>
+        <v>1607</v>
       </c>
       <c r="K73" t="n">
         <v>-0</v>
@@ -40551,7 +40551,7 @@
         <v>19596.6816</v>
       </c>
       <c r="J74" t="n">
-        <v>-0</v>
+        <v>1607</v>
       </c>
       <c r="K74" t="n">
         <v>-0</v>
@@ -40880,7 +40880,7 @@
         <v>18699.6504</v>
       </c>
       <c r="J81" t="n">
-        <v>-0</v>
+        <v>854.2396409426958</v>
       </c>
       <c r="K81" t="n">
         <v>-0</v>
@@ -40927,7 +40927,7 @@
         <v>16284.5664</v>
       </c>
       <c r="J82" t="n">
-        <v>1607</v>
+        <v>-0</v>
       </c>
       <c r="K82" t="n">
         <v>-0</v>
@@ -40974,7 +40974,7 @@
         <v>9384.3264</v>
       </c>
       <c r="J83" t="n">
-        <v>1607</v>
+        <v>1369.969277758229</v>
       </c>
       <c r="K83" t="n">
         <v>-0</v>
@@ -41679,7 +41679,7 @@
         <v>19148.166</v>
       </c>
       <c r="J98" t="n">
-        <v>-0</v>
+        <v>1607</v>
       </c>
       <c r="K98" t="n">
         <v>-0</v>
@@ -42143,7 +42143,7 @@
         <v>18923.89044</v>
       </c>
       <c r="H108" t="n">
-        <v>20117.53566655577</v>
+        <v>21161.01392742534</v>
       </c>
       <c r="I108" t="n">
         <v>-0</v>
@@ -42190,7 +42190,7 @@
         <v>20291.88252</v>
       </c>
       <c r="H109" t="n">
-        <v>22437.56798143708</v>
+        <v>21394.08972056752</v>
       </c>
       <c r="I109" t="n">
         <v>-0</v>
@@ -42540,7 +42540,7 @@
         <v>2073.698</v>
       </c>
       <c r="O116" t="n">
-        <v>5034.351248745426</v>
+        <v>4074.351248745427</v>
       </c>
     </row>
     <row r="117">
@@ -42587,7 +42587,7 @@
         <v>2391.202</v>
       </c>
       <c r="O117" t="n">
-        <v>3686.592042639748</v>
+        <v>4810.643530034884</v>
       </c>
     </row>
     <row r="118">
@@ -42681,7 +42681,7 @@
         <v>3423.09</v>
       </c>
       <c r="O119" t="n">
-        <v>164.0514873951365</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="120">
@@ -42807,7 +42807,7 @@
         <v>17595.612</v>
       </c>
       <c r="J122" t="n">
-        <v>1607</v>
+        <v>89.36786909033724</v>
       </c>
       <c r="K122" t="n">
         <v>-0</v>
@@ -43042,7 +43042,7 @@
         <v>17388.6048</v>
       </c>
       <c r="J127" t="n">
-        <v>1607</v>
+        <v>-0</v>
       </c>
       <c r="K127" t="n">
         <v>-0</v>
@@ -43271,7 +43271,7 @@
         <v>25953.84974</v>
       </c>
       <c r="H132" t="n">
-        <v>21664.49896955841</v>
+        <v>20621.02070868884</v>
       </c>
       <c r="I132" t="n">
         <v>4968.172799999999</v>
@@ -43318,7 +43318,7 @@
         <v>23597.86338</v>
       </c>
       <c r="H133" t="n">
-        <v>24379.81923334638</v>
+        <v>25423.29749421595</v>
       </c>
       <c r="I133" t="n">
         <v>-0</v>
@@ -43488,7 +43488,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>24280.4277316089</v>
+        <v>9994.713445894617</v>
       </c>
       <c r="C137" t="n">
         <v>-0</v>
@@ -44055,7 +44055,7 @@
         <v>-0</v>
       </c>
       <c r="C149" t="n">
-        <v>16604.67605205733</v>
+        <v>13316.10175332801</v>
       </c>
       <c r="D149" t="n">
         <v>-0</v>
@@ -44854,7 +44854,7 @@
         <v>-0</v>
       </c>
       <c r="C166" t="n">
-        <v>46461.43435478492</v>
+        <v>49757.9279236976</v>
       </c>
       <c r="D166" t="n">
         <v>-0</v>
@@ -44901,7 +44901,7 @@
         <v>-0</v>
       </c>
       <c r="C167" t="n">
-        <v>50907.36017835532</v>
+        <v>62589.64716121246</v>
       </c>
       <c r="D167" t="n">
         <v>-0</v>
@@ -44948,7 +44948,7 @@
         <v>-0</v>
       </c>
       <c r="C168" t="n">
-        <v>65432.00257197711</v>
+        <v>77235.56378626282</v>
       </c>
       <c r="D168" t="n">
         <v>-0</v>
@@ -44995,7 +44995,7 @@
         <v>-0</v>
       </c>
       <c r="C169" t="n">
-        <v>59646.82149670718</v>
+        <v>73932.53578242147</v>
       </c>
       <c r="D169" t="n">
         <v>-0</v>
@@ -45016,7 +45016,7 @@
         <v>23184.8064</v>
       </c>
       <c r="J169" t="n">
-        <v>1607</v>
+        <v>865.6334208970314</v>
       </c>
       <c r="K169" t="n">
         <v>-0</v>
@@ -45276,7 +45276,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>3083.729786430806</v>
       </c>
     </row>
     <row r="3">
@@ -45284,7 +45284,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>-1262.104345983993</v>
       </c>
     </row>
     <row r="4">
@@ -45292,7 +45292,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-2312.803088345798</v>
+        <v>-2877.75</v>
       </c>
     </row>
     <row r="5">
@@ -45300,7 +45300,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-2877.75</v>
+        <v>-2668.870101756987</v>
       </c>
     </row>
     <row r="6">
@@ -45332,7 +45332,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-1898.995868396093</v>
+        <v>-2134.206896571862</v>
       </c>
     </row>
     <row r="10">
@@ -45508,7 +45508,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>-0</v>
+        <v>-1998.240915047859</v>
       </c>
     </row>
     <row r="32">
@@ -45596,7 +45596,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>-2544.447508239384</v>
+        <v>-128.3325476603845</v>
       </c>
     </row>
     <row r="43">
@@ -45620,7 +45620,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>-0</v>
+        <v>-2841.468617029268</v>
       </c>
     </row>
     <row r="46">
@@ -45636,7 +45636,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>-2877.75</v>
+        <v>-2400.289799508634</v>
       </c>
     </row>
     <row r="48">
@@ -45644,7 +45644,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>-2877.75</v>
+        <v>-2215.902425830639</v>
       </c>
     </row>
     <row r="49">
@@ -45804,7 +45804,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>7148.066353688082</v>
+        <v>7604.9</v>
       </c>
     </row>
     <row r="69">
@@ -45812,7 +45812,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>6028.163934888532</v>
+        <v>5571.330288576614</v>
       </c>
     </row>
     <row r="70">
@@ -45844,7 +45844,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>-0</v>
+        <v>-1177.402945502321</v>
       </c>
     </row>
     <row r="74">
@@ -45852,7 +45852,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>-703.5990098711518</v>
+        <v>-1908.849009871152</v>
       </c>
     </row>
     <row r="75">
@@ -45908,7 +45908,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>-1660.759683868219</v>
+        <v>-2877.75</v>
       </c>
     </row>
     <row r="82">
@@ -45916,7 +45916,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>-1143.9669761236</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="83">
@@ -45924,7 +45924,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>-815.3666509824874</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="84">
@@ -46004,7 +46004,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>6095.794777803401</v>
+        <v>7604.9</v>
       </c>
     </row>
     <row r="94">
@@ -46028,7 +46028,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>2753.729489753548</v>
+        <v>1244.624267556949</v>
       </c>
     </row>
     <row r="97">
@@ -46044,7 +46044,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>-1300.975546777526</v>
+        <v>-2506.225546777526</v>
       </c>
     </row>
     <row r="99">
@@ -46236,7 +46236,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>-1166.856002693494</v>
+        <v>-28.63190451124683</v>
       </c>
     </row>
     <row r="123">
@@ -46244,7 +46244,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>-268.5585927010036</v>
+        <v>-1936.471937077471</v>
       </c>
     </row>
     <row r="124">
@@ -46276,7 +46276,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>-2873.163344376467</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="128">
@@ -46364,7 +46364,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>5461.699245228119</v>
+        <v>3061.699245228117</v>
       </c>
     </row>
     <row r="139">
@@ -46396,7 +46396,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>5121.321697167798</v>
+        <v>7521.321697167798</v>
       </c>
     </row>
     <row r="143">
@@ -46444,7 +46444,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>1254.120081118349</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="149">
@@ -46460,7 +46460,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>795.7164574239072</v>
+        <v>2403.586865048359</v>
       </c>
     </row>
     <row r="151">
@@ -46476,7 +46476,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>658.594417483028</v>
+        <v>3819.657035759352</v>
       </c>
     </row>
     <row r="153">
@@ -46484,7 +46484,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>7604.9</v>
+        <v>4090.087055217573</v>
       </c>
     </row>
     <row r="154">
@@ -46612,7 +46612,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>-556.024934327226</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
@@ -46649,7 +46649,7 @@
         <v>277536800</v>
       </c>
       <c r="C2" t="n">
-        <v>692733.0814108214</v>
+        <v>2917121.014120428</v>
       </c>
     </row>
     <row r="3">
@@ -46660,7 +46660,7 @@
         <v>277536800</v>
       </c>
       <c r="C3" t="n">
-        <v>692733.0814108214</v>
+        <v>2918383.118466412</v>
       </c>
     </row>
     <row r="4">
@@ -46671,7 +46671,7 @@
         <v>277536800</v>
       </c>
       <c r="C4" t="n">
-        <v>695045.8844991672</v>
+        <v>2921260.868466412</v>
       </c>
     </row>
     <row r="5">
@@ -46682,7 +46682,7 @@
         <v>277536800</v>
       </c>
       <c r="C5" t="n">
-        <v>697923.6344991672</v>
+        <v>2923929.738568169</v>
       </c>
     </row>
     <row r="6">
@@ -46693,7 +46693,7 @@
         <v>277536800</v>
       </c>
       <c r="C6" t="n">
-        <v>700801.3844991672</v>
+        <v>2926807.488568169</v>
       </c>
     </row>
     <row r="7">
@@ -46704,7 +46704,7 @@
         <v>277536800</v>
       </c>
       <c r="C7" t="n">
-        <v>703679.1344991672</v>
+        <v>2929685.238568169</v>
       </c>
     </row>
     <row r="8">
@@ -46715,7 +46715,7 @@
         <v>277536800</v>
       </c>
       <c r="C8" t="n">
-        <v>706556.8844991672</v>
+        <v>2932562.988568169</v>
       </c>
     </row>
     <row r="9">
@@ -46726,7 +46726,7 @@
         <v>277536800</v>
       </c>
       <c r="C9" t="n">
-        <v>708455.8803675633</v>
+        <v>2934697.195464741</v>
       </c>
     </row>
     <row r="10">
@@ -46737,7 +46737,7 @@
         <v>277536800</v>
       </c>
       <c r="C10" t="n">
-        <v>711333.6303675633</v>
+        <v>2937574.945464741</v>
       </c>
     </row>
     <row r="11">
@@ -46748,7 +46748,7 @@
         <v>277536800</v>
       </c>
       <c r="C11" t="n">
-        <v>714211.3803675633</v>
+        <v>2940452.695464741</v>
       </c>
     </row>
     <row r="12">
@@ -46759,7 +46759,7 @@
         <v>277536800</v>
       </c>
       <c r="C12" t="n">
-        <v>717089.1303675633</v>
+        <v>2943330.445464741</v>
       </c>
     </row>
     <row r="13">
@@ -46770,7 +46770,7 @@
         <v>277536800</v>
       </c>
       <c r="C13" t="n">
-        <v>719966.8803675633</v>
+        <v>2946208.195464741</v>
       </c>
     </row>
     <row r="14">
@@ -46781,7 +46781,7 @@
         <v>277536800</v>
       </c>
       <c r="C14" t="n">
-        <v>722844.6303675633</v>
+        <v>2949085.945464741</v>
       </c>
     </row>
     <row r="15">
@@ -46792,7 +46792,7 @@
         <v>277536800</v>
       </c>
       <c r="C15" t="n">
-        <v>725722.3803675633</v>
+        <v>2951963.695464741</v>
       </c>
     </row>
     <row r="16">
@@ -46803,7 +46803,7 @@
         <v>277536800</v>
       </c>
       <c r="C16" t="n">
-        <v>728600.1303675633</v>
+        <v>2954841.445464741</v>
       </c>
     </row>
     <row r="17">
@@ -46814,7 +46814,7 @@
         <v>277536800</v>
       </c>
       <c r="C17" t="n">
-        <v>731477.8803675633</v>
+        <v>2957719.195464741</v>
       </c>
     </row>
     <row r="18">
@@ -46825,7 +46825,7 @@
         <v>277536800</v>
       </c>
       <c r="C18" t="n">
-        <v>727350.5565695519</v>
+        <v>2953591.871666729</v>
       </c>
     </row>
     <row r="19">
@@ -46836,7 +46836,7 @@
         <v>277536800</v>
       </c>
       <c r="C19" t="n">
-        <v>719745.6565695519</v>
+        <v>2945986.971666729</v>
       </c>
     </row>
     <row r="20">
@@ -46847,7 +46847,7 @@
         <v>277536800</v>
       </c>
       <c r="C20" t="n">
-        <v>712140.7565695519</v>
+        <v>2938382.071666729</v>
       </c>
     </row>
     <row r="21">
@@ -46858,7 +46858,7 @@
         <v>277536800</v>
       </c>
       <c r="C21" t="n">
-        <v>704535.8565695519</v>
+        <v>2930777.171666729</v>
       </c>
     </row>
     <row r="22">
@@ -46869,7 +46869,7 @@
         <v>277536800</v>
       </c>
       <c r="C22" t="n">
-        <v>696930.9565695518</v>
+        <v>2923172.271666729</v>
       </c>
     </row>
     <row r="23">
@@ -46880,7 +46880,7 @@
         <v>277536800</v>
       </c>
       <c r="C23" t="n">
-        <v>689326.0565695518</v>
+        <v>2915567.371666729</v>
       </c>
     </row>
     <row r="24">
@@ -46891,7 +46891,7 @@
         <v>277536800</v>
       </c>
       <c r="C24" t="n">
-        <v>681721.1565695518</v>
+        <v>2907962.47166673</v>
       </c>
     </row>
     <row r="25">
@@ -46902,7 +46902,7 @@
         <v>277536800</v>
       </c>
       <c r="C25" t="n">
-        <v>674116.2565695518</v>
+        <v>2900357.57166673</v>
       </c>
     </row>
     <row r="26">
@@ -46913,7 +46913,7 @@
         <v>277536800</v>
       </c>
       <c r="C26" t="n">
-        <v>666511.3565695517</v>
+        <v>2892752.67166673</v>
       </c>
     </row>
     <row r="27">
@@ -46924,7 +46924,7 @@
         <v>277536800</v>
       </c>
       <c r="C27" t="n">
-        <v>663509.4824651028</v>
+        <v>2889750.797562281</v>
       </c>
     </row>
     <row r="28">
@@ -46935,7 +46935,7 @@
         <v>277536800</v>
       </c>
       <c r="C28" t="n">
-        <v>663509.4824651028</v>
+        <v>2889750.797562281</v>
       </c>
     </row>
     <row r="29">
@@ -46946,7 +46946,7 @@
         <v>277536800</v>
       </c>
       <c r="C29" t="n">
-        <v>663509.4824651028</v>
+        <v>2889750.797562281</v>
       </c>
     </row>
     <row r="30">
@@ -46957,7 +46957,7 @@
         <v>277536800</v>
       </c>
       <c r="C30" t="n">
-        <v>663509.4824651028</v>
+        <v>2889750.797562281</v>
       </c>
     </row>
     <row r="31">
@@ -46968,7 +46968,7 @@
         <v>277536800</v>
       </c>
       <c r="C31" t="n">
-        <v>663509.4824651028</v>
+        <v>2891749.038477329</v>
       </c>
     </row>
     <row r="32">
@@ -46979,7 +46979,7 @@
         <v>277536800</v>
       </c>
       <c r="C32" t="n">
-        <v>663509.4824651028</v>
+        <v>2891749.038477329</v>
       </c>
     </row>
     <row r="33">
@@ -46990,7 +46990,7 @@
         <v>277536800</v>
       </c>
       <c r="C33" t="n">
-        <v>661520</v>
+        <v>2889759.556012226</v>
       </c>
     </row>
     <row r="34">
@@ -47001,7 +47001,7 @@
         <v>277536800</v>
       </c>
       <c r="C34" t="n">
-        <v>662797.3394511829</v>
+        <v>2891036.895463409</v>
       </c>
     </row>
     <row r="35">
@@ -47012,7 +47012,7 @@
         <v>277536800</v>
       </c>
       <c r="C35" t="n">
-        <v>665675.0894511829</v>
+        <v>2893914.645463409</v>
       </c>
     </row>
     <row r="36">
@@ -47023,7 +47023,7 @@
         <v>277536800</v>
       </c>
       <c r="C36" t="n">
-        <v>668552.8394511829</v>
+        <v>2896792.395463409</v>
       </c>
     </row>
     <row r="37">
@@ -47034,7 +47034,7 @@
         <v>277536800</v>
       </c>
       <c r="C37" t="n">
-        <v>671430.5894511829</v>
+        <v>2899670.145463409</v>
       </c>
     </row>
     <row r="38">
@@ -47045,7 +47045,7 @@
         <v>277536800</v>
       </c>
       <c r="C38" t="n">
-        <v>674308.3394511829</v>
+        <v>2902547.895463409</v>
       </c>
     </row>
     <row r="39">
@@ -47056,7 +47056,7 @@
         <v>277536800</v>
       </c>
       <c r="C39" t="n">
-        <v>677186.0894511829</v>
+        <v>2905425.645463409</v>
       </c>
     </row>
     <row r="40">
@@ -47067,7 +47067,7 @@
         <v>277536800</v>
       </c>
       <c r="C40" t="n">
-        <v>680063.8394511829</v>
+        <v>2908303.395463409</v>
       </c>
     </row>
     <row r="41">
@@ -47078,7 +47078,7 @@
         <v>277536800</v>
       </c>
       <c r="C41" t="n">
-        <v>682941.5894511829</v>
+        <v>2911181.145463409</v>
       </c>
     </row>
     <row r="42">
@@ -47089,7 +47089,7 @@
         <v>277536800</v>
       </c>
       <c r="C42" t="n">
-        <v>685486.0369594223</v>
+        <v>2911309.478011069</v>
       </c>
     </row>
     <row r="43">
@@ -47100,7 +47100,7 @@
         <v>277536800</v>
       </c>
       <c r="C43" t="n">
-        <v>679335.6495738407</v>
+        <v>2905159.090625488</v>
       </c>
     </row>
     <row r="44">
@@ -47111,7 +47111,7 @@
         <v>277536800</v>
       </c>
       <c r="C44" t="n">
-        <v>679335.6495738407</v>
+        <v>2905159.090625488</v>
       </c>
     </row>
     <row r="45">
@@ -47122,7 +47122,7 @@
         <v>277536800</v>
       </c>
       <c r="C45" t="n">
-        <v>679335.6495738407</v>
+        <v>2908000.559242517</v>
       </c>
     </row>
     <row r="46">
@@ -47133,7 +47133,7 @@
         <v>277536800</v>
       </c>
       <c r="C46" t="n">
-        <v>679335.6495738407</v>
+        <v>2908000.559242517</v>
       </c>
     </row>
     <row r="47">
@@ -47144,7 +47144,7 @@
         <v>277536800</v>
       </c>
       <c r="C47" t="n">
-        <v>682213.3995738407</v>
+        <v>2910400.849042026</v>
       </c>
     </row>
     <row r="48">
@@ -47155,7 +47155,7 @@
         <v>277536800</v>
       </c>
       <c r="C48" t="n">
-        <v>685091.1495738407</v>
+        <v>2912616.751467857</v>
       </c>
     </row>
     <row r="49">
@@ -47166,7 +47166,7 @@
         <v>277536800</v>
       </c>
       <c r="C49" t="n">
-        <v>687968.8995738407</v>
+        <v>2915494.501467857</v>
       </c>
     </row>
     <row r="50">
@@ -47177,7 +47177,7 @@
         <v>277536800</v>
       </c>
       <c r="C50" t="n">
-        <v>690846.6495738407</v>
+        <v>2918372.251467857</v>
       </c>
     </row>
     <row r="51">
@@ -47188,7 +47188,7 @@
         <v>277536800</v>
       </c>
       <c r="C51" t="n">
-        <v>693724.3995738407</v>
+        <v>2921250.001467857</v>
       </c>
     </row>
     <row r="52">
@@ -47199,7 +47199,7 @@
         <v>277536800</v>
       </c>
       <c r="C52" t="n">
-        <v>696602.1495738407</v>
+        <v>2924127.751467857</v>
       </c>
     </row>
     <row r="53">
@@ -47210,7 +47210,7 @@
         <v>277536800</v>
       </c>
       <c r="C53" t="n">
-        <v>699479.8995738407</v>
+        <v>2927005.501467857</v>
       </c>
     </row>
     <row r="54">
@@ -47221,7 +47221,7 @@
         <v>277536800</v>
       </c>
       <c r="C54" t="n">
-        <v>702357.6495738407</v>
+        <v>2929883.251467857</v>
       </c>
     </row>
     <row r="55">
@@ -47232,7 +47232,7 @@
         <v>277536800</v>
       </c>
       <c r="C55" t="n">
-        <v>705235.3995738407</v>
+        <v>2932761.001467857</v>
       </c>
     </row>
     <row r="56">
@@ -47243,7 +47243,7 @@
         <v>277536800</v>
       </c>
       <c r="C56" t="n">
-        <v>708113.1495738407</v>
+        <v>2935638.751467857</v>
       </c>
     </row>
     <row r="57">
@@ -47254,7 +47254,7 @@
         <v>277536800</v>
       </c>
       <c r="C57" t="n">
-        <v>710990.8995738407</v>
+        <v>2938516.501467857</v>
       </c>
     </row>
     <row r="58">
@@ -47265,7 +47265,7 @@
         <v>277536800</v>
       </c>
       <c r="C58" t="n">
-        <v>713868.6495738407</v>
+        <v>2941394.251467857</v>
       </c>
     </row>
     <row r="59">
@@ -47276,7 +47276,7 @@
         <v>277536800</v>
       </c>
       <c r="C59" t="n">
-        <v>716746.3995738407</v>
+        <v>2944272.001467857</v>
       </c>
     </row>
     <row r="60">
@@ -47287,7 +47287,7 @@
         <v>277536800</v>
       </c>
       <c r="C60" t="n">
-        <v>719624.1495738407</v>
+        <v>2947149.751467857</v>
       </c>
     </row>
     <row r="61">
@@ -47298,7 +47298,7 @@
         <v>277536800</v>
       </c>
       <c r="C61" t="n">
-        <v>722501.8995738407</v>
+        <v>2950027.501467857</v>
       </c>
     </row>
     <row r="62">
@@ -47309,7 +47309,7 @@
         <v>277536800</v>
       </c>
       <c r="C62" t="n">
-        <v>725379.6495738407</v>
+        <v>2952905.251467857</v>
       </c>
     </row>
     <row r="63">
@@ -47320,7 +47320,7 @@
         <v>277536800</v>
       </c>
       <c r="C63" t="n">
-        <v>728257.3995738407</v>
+        <v>2955783.001467857</v>
       </c>
     </row>
     <row r="64">
@@ -47331,7 +47331,7 @@
         <v>277536800</v>
       </c>
       <c r="C64" t="n">
-        <v>731135.1495738407</v>
+        <v>2958660.751467857</v>
       </c>
     </row>
     <row r="65">
@@ -47342,7 +47342,7 @@
         <v>277536800</v>
       </c>
       <c r="C65" t="n">
-        <v>734012.8995738407</v>
+        <v>2961538.501467857</v>
       </c>
     </row>
     <row r="66">
@@ -47353,7 +47353,7 @@
         <v>277536800</v>
       </c>
       <c r="C66" t="n">
-        <v>734012.8995738407</v>
+        <v>2961538.501467857</v>
       </c>
     </row>
     <row r="67">
@@ -47364,7 +47364,7 @@
         <v>277536800</v>
       </c>
       <c r="C67" t="n">
-        <v>726407.9995738406</v>
+        <v>2953933.601467857</v>
       </c>
     </row>
     <row r="68">
@@ -47375,7 +47375,7 @@
         <v>277536800</v>
       </c>
       <c r="C68" t="n">
-        <v>719259.9332201525</v>
+        <v>2946328.701467857</v>
       </c>
     </row>
     <row r="69">
@@ -47386,7 +47386,7 @@
         <v>277536800</v>
       </c>
       <c r="C69" t="n">
-        <v>713231.769285264</v>
+        <v>2940757.37117928</v>
       </c>
     </row>
     <row r="70">
@@ -47397,7 +47397,7 @@
         <v>277536800</v>
       </c>
       <c r="C70" t="n">
-        <v>711054.7647341084</v>
+        <v>2938580.366628125</v>
       </c>
     </row>
     <row r="71">
@@ -47408,7 +47408,7 @@
         <v>277536800</v>
       </c>
       <c r="C71" t="n">
-        <v>708309.8087919778</v>
+        <v>2935835.410685994</v>
       </c>
     </row>
     <row r="72">
@@ -47419,7 +47419,7 @@
         <v>277536800</v>
       </c>
       <c r="C72" t="n">
-        <v>708567.1698905134</v>
+        <v>2936092.77178453</v>
       </c>
     </row>
     <row r="73">
@@ -47430,7 +47430,7 @@
         <v>277536800</v>
       </c>
       <c r="C73" t="n">
-        <v>708567.1698905134</v>
+        <v>2937270.174730032</v>
       </c>
     </row>
     <row r="74">
@@ -47441,7 +47441,7 @@
         <v>277536800</v>
       </c>
       <c r="C74" t="n">
-        <v>709270.7689003845</v>
+        <v>2939179.023739903</v>
       </c>
     </row>
     <row r="75">
@@ -47452,7 +47452,7 @@
         <v>277536800</v>
       </c>
       <c r="C75" t="n">
-        <v>712127.0954957743</v>
+        <v>2942035.350335293</v>
       </c>
     </row>
     <row r="76">
@@ -47463,7 +47463,7 @@
         <v>277536800</v>
       </c>
       <c r="C76" t="n">
-        <v>714538.6884684635</v>
+        <v>2944446.943307982</v>
       </c>
     </row>
     <row r="77">
@@ -47474,7 +47474,7 @@
         <v>277536800</v>
       </c>
       <c r="C77" t="n">
-        <v>717051.2828509373</v>
+        <v>2946959.537690456</v>
       </c>
     </row>
     <row r="78">
@@ -47485,7 +47485,7 @@
         <v>277536800</v>
       </c>
       <c r="C78" t="n">
-        <v>719929.0328509373</v>
+        <v>2949837.287690456</v>
       </c>
     </row>
     <row r="79">
@@ -47496,7 +47496,7 @@
         <v>277536800</v>
       </c>
       <c r="C79" t="n">
-        <v>722806.7828509373</v>
+        <v>2952715.037690456</v>
       </c>
     </row>
     <row r="80">
@@ -47507,7 +47507,7 @@
         <v>277536800</v>
       </c>
       <c r="C80" t="n">
-        <v>725684.5328509373</v>
+        <v>2955592.787690456</v>
       </c>
     </row>
     <row r="81">
@@ -47518,7 +47518,7 @@
         <v>277536800</v>
       </c>
       <c r="C81" t="n">
-        <v>727345.2925348056</v>
+        <v>2958470.537690456</v>
       </c>
     </row>
     <row r="82">
@@ -47529,7 +47529,7 @@
         <v>277536800</v>
       </c>
       <c r="C82" t="n">
-        <v>728489.2595109292</v>
+        <v>2958470.537690456</v>
       </c>
     </row>
     <row r="83">
@@ -47540,7 +47540,7 @@
         <v>277536800</v>
       </c>
       <c r="C83" t="n">
-        <v>729304.6261619118</v>
+        <v>2958470.537690456</v>
       </c>
     </row>
     <row r="84">
@@ -47551,7 +47551,7 @@
         <v>277536800</v>
       </c>
       <c r="C84" t="n">
-        <v>732182.3761619118</v>
+        <v>2961348.287690456</v>
       </c>
     </row>
     <row r="85">
@@ -47562,7 +47562,7 @@
         <v>277536800</v>
       </c>
       <c r="C85" t="n">
-        <v>735060.1261619118</v>
+        <v>2964226.037690456</v>
       </c>
     </row>
     <row r="86">
@@ -47573,7 +47573,7 @@
         <v>277536800</v>
       </c>
       <c r="C86" t="n">
-        <v>737937.8761619118</v>
+        <v>2967103.787690456</v>
       </c>
     </row>
     <row r="87">
@@ -47584,7 +47584,7 @@
         <v>277536800</v>
       </c>
       <c r="C87" t="n">
-        <v>740815.6261619118</v>
+        <v>2969981.537690456</v>
       </c>
     </row>
     <row r="88">
@@ -47595,7 +47595,7 @@
         <v>277536800</v>
       </c>
       <c r="C88" t="n">
-        <v>743693.3761619118</v>
+        <v>2972859.287690456</v>
       </c>
     </row>
     <row r="89">
@@ -47606,7 +47606,7 @@
         <v>277536800</v>
       </c>
       <c r="C89" t="n">
-        <v>743693.3761619118</v>
+        <v>2972859.287690456</v>
       </c>
     </row>
     <row r="90">
@@ -47617,7 +47617,7 @@
         <v>277536800</v>
       </c>
       <c r="C90" t="n">
-        <v>736088.4761619117</v>
+        <v>2965254.387690456</v>
       </c>
     </row>
     <row r="91">
@@ -47628,7 +47628,7 @@
         <v>277536800</v>
       </c>
       <c r="C91" t="n">
-        <v>728483.5761619117</v>
+        <v>2957649.487690456</v>
       </c>
     </row>
     <row r="92">
@@ -47639,7 +47639,7 @@
         <v>277536800</v>
       </c>
       <c r="C92" t="n">
-        <v>720878.6761619117</v>
+        <v>2950044.587690456</v>
       </c>
     </row>
     <row r="93">
@@ -47650,7 +47650,7 @@
         <v>277536800</v>
       </c>
       <c r="C93" t="n">
-        <v>714782.8813841083</v>
+        <v>2942439.687690456</v>
       </c>
     </row>
     <row r="94">
@@ -47661,7 +47661,7 @@
         <v>277536800</v>
       </c>
       <c r="C94" t="n">
-        <v>708925.28523537</v>
+        <v>2936582.091541718</v>
       </c>
     </row>
     <row r="95">
@@ -47672,7 +47672,7 @@
         <v>277536800</v>
       </c>
       <c r="C95" t="n">
-        <v>704755.342414432</v>
+        <v>2932412.148720779</v>
       </c>
     </row>
     <row r="96">
@@ -47683,7 +47683,7 @@
         <v>277536800</v>
       </c>
       <c r="C96" t="n">
-        <v>702001.6129246784</v>
+        <v>2931167.524453222</v>
       </c>
     </row>
     <row r="97">
@@ -47694,7 +47694,7 @@
         <v>277536800</v>
       </c>
       <c r="C97" t="n">
-        <v>702001.6129246784</v>
+        <v>2931167.524453222</v>
       </c>
     </row>
     <row r="98">
@@ -47705,7 +47705,7 @@
         <v>277536800</v>
       </c>
       <c r="C98" t="n">
-        <v>703302.5884714558</v>
+        <v>2933673.75</v>
       </c>
     </row>
     <row r="99">
@@ -47716,7 +47716,7 @@
         <v>277536800</v>
       </c>
       <c r="C99" t="n">
-        <v>706180.3384714558</v>
+        <v>2936551.5</v>
       </c>
     </row>
     <row r="100">
@@ -47727,7 +47727,7 @@
         <v>277536800</v>
       </c>
       <c r="C100" t="n">
-        <v>709058.0884714558</v>
+        <v>2939429.25</v>
       </c>
     </row>
     <row r="101">
@@ -47738,7 +47738,7 @@
         <v>277536800</v>
       </c>
       <c r="C101" t="n">
-        <v>711935.8384714558</v>
+        <v>2942307</v>
       </c>
     </row>
     <row r="102">
@@ -47749,7 +47749,7 @@
         <v>277536800</v>
       </c>
       <c r="C102" t="n">
-        <v>714813.5884714558</v>
+        <v>2945184.75</v>
       </c>
     </row>
     <row r="103">
@@ -47760,7 +47760,7 @@
         <v>277536800</v>
       </c>
       <c r="C103" t="n">
-        <v>717691.3384714558</v>
+        <v>2948062.5</v>
       </c>
     </row>
     <row r="104">
@@ -47771,7 +47771,7 @@
         <v>277536800</v>
       </c>
       <c r="C104" t="n">
-        <v>720569.0884714558</v>
+        <v>2950940.25</v>
       </c>
     </row>
     <row r="105">
@@ -47782,7 +47782,7 @@
         <v>277536800</v>
       </c>
       <c r="C105" t="n">
-        <v>723446.8384714558</v>
+        <v>2953818</v>
       </c>
     </row>
     <row r="106">
@@ -47793,7 +47793,7 @@
         <v>277536800</v>
       </c>
       <c r="C106" t="n">
-        <v>726324.5884714558</v>
+        <v>2956695.75</v>
       </c>
     </row>
     <row r="107">
@@ -47804,7 +47804,7 @@
         <v>277536800</v>
       </c>
       <c r="C107" t="n">
-        <v>729202.3384714558</v>
+        <v>2959573.5</v>
       </c>
     </row>
     <row r="108">
@@ -47815,7 +47815,7 @@
         <v>277536800</v>
       </c>
       <c r="C108" t="n">
-        <v>732080.0884714558</v>
+        <v>2962451.25</v>
       </c>
     </row>
     <row r="109">
@@ -47826,7 +47826,7 @@
         <v>277536800</v>
       </c>
       <c r="C109" t="n">
-        <v>734957.8384714558</v>
+        <v>2965329</v>
       </c>
     </row>
     <row r="110">
@@ -47837,7 +47837,7 @@
         <v>277536800</v>
       </c>
       <c r="C110" t="n">
-        <v>737835.5884714558</v>
+        <v>2968206.75</v>
       </c>
     </row>
     <row r="111">
@@ -47848,7 +47848,7 @@
         <v>277536800</v>
       </c>
       <c r="C111" t="n">
-        <v>740713.3384714558</v>
+        <v>2971084.5</v>
       </c>
     </row>
     <row r="112">
@@ -47859,7 +47859,7 @@
         <v>277536800</v>
       </c>
       <c r="C112" t="n">
-        <v>743591.0884714558</v>
+        <v>2973962.25</v>
       </c>
     </row>
     <row r="113">
@@ -47870,7 +47870,7 @@
         <v>277536800</v>
       </c>
       <c r="C113" t="n">
-        <v>746468.8384714558</v>
+        <v>2976840</v>
       </c>
     </row>
     <row r="114">
@@ -47881,7 +47881,7 @@
         <v>277536800</v>
       </c>
       <c r="C114" t="n">
-        <v>744114.0007222008</v>
+        <v>2974485.162250745</v>
       </c>
     </row>
     <row r="115">
@@ -47892,7 +47892,7 @@
         <v>277536800</v>
       </c>
       <c r="C115" t="n">
-        <v>736509.1007222008</v>
+        <v>2966880.262250745</v>
       </c>
     </row>
     <row r="116">
@@ -47903,7 +47903,7 @@
         <v>277536800</v>
       </c>
       <c r="C116" t="n">
-        <v>728904.2007222008</v>
+        <v>2959275.362250745</v>
       </c>
     </row>
     <row r="117">
@@ -47914,7 +47914,7 @@
         <v>277536800</v>
       </c>
       <c r="C117" t="n">
-        <v>721299.3007222008</v>
+        <v>2951670.462250745</v>
       </c>
     </row>
     <row r="118">
@@ -47925,7 +47925,7 @@
         <v>277536800</v>
       </c>
       <c r="C118" t="n">
-        <v>713694.4007222007</v>
+        <v>2944065.562250745</v>
       </c>
     </row>
     <row r="119">
@@ -47936,7 +47936,7 @@
         <v>277536800</v>
       </c>
       <c r="C119" t="n">
-        <v>706089.5007222007</v>
+        <v>2936460.662250746</v>
       </c>
     </row>
     <row r="120">
@@ -47947,7 +47947,7 @@
         <v>277536800</v>
       </c>
       <c r="C120" t="n">
-        <v>698484.6007222007</v>
+        <v>2928855.762250746</v>
       </c>
     </row>
     <row r="121">
@@ -47958,7 +47958,7 @@
         <v>277536800</v>
       </c>
       <c r="C121" t="n">
-        <v>696675.5548248163</v>
+        <v>2927046.716353361</v>
       </c>
     </row>
     <row r="122">
@@ -47969,7 +47969,7 @@
         <v>277536800</v>
       </c>
       <c r="C122" t="n">
-        <v>697842.4108275098</v>
+        <v>2927075.348257873</v>
       </c>
     </row>
     <row r="123">
@@ -47980,7 +47980,7 @@
         <v>277536800</v>
       </c>
       <c r="C123" t="n">
-        <v>698110.9694202108</v>
+        <v>2929011.82019495</v>
       </c>
     </row>
     <row r="124">
@@ -47991,7 +47991,7 @@
         <v>277536800</v>
       </c>
       <c r="C124" t="n">
-        <v>700988.7194202108</v>
+        <v>2931889.57019495</v>
       </c>
     </row>
     <row r="125">
@@ -48002,7 +48002,7 @@
         <v>277536800</v>
       </c>
       <c r="C125" t="n">
-        <v>703866.4694202108</v>
+        <v>2934767.32019495</v>
       </c>
     </row>
     <row r="126">
@@ -48013,7 +48013,7 @@
         <v>277536800</v>
       </c>
       <c r="C126" t="n">
-        <v>706575.0247148809</v>
+        <v>2937475.87548962</v>
       </c>
     </row>
     <row r="127">
@@ -48024,7 +48024,7 @@
         <v>277536800</v>
       </c>
       <c r="C127" t="n">
-        <v>709448.1880592573</v>
+        <v>2937475.87548962</v>
       </c>
     </row>
     <row r="128">
@@ -48035,7 +48035,7 @@
         <v>277536800</v>
       </c>
       <c r="C128" t="n">
-        <v>709448.1880592573</v>
+        <v>2937475.87548962</v>
       </c>
     </row>
     <row r="129">
@@ -48046,7 +48046,7 @@
         <v>277536800</v>
       </c>
       <c r="C129" t="n">
-        <v>709448.1880592573</v>
+        <v>2937475.87548962</v>
       </c>
     </row>
     <row r="130">
@@ -48057,7 +48057,7 @@
         <v>277536800</v>
       </c>
       <c r="C130" t="n">
-        <v>712325.9380592573</v>
+        <v>2940353.62548962</v>
       </c>
     </row>
     <row r="131">
@@ -48068,7 +48068,7 @@
         <v>277536800</v>
       </c>
       <c r="C131" t="n">
-        <v>715203.6880592573</v>
+        <v>2943231.37548962</v>
       </c>
     </row>
     <row r="132">
@@ -48079,7 +48079,7 @@
         <v>277536800</v>
       </c>
       <c r="C132" t="n">
-        <v>718081.4380592573</v>
+        <v>2946109.12548962</v>
       </c>
     </row>
     <row r="133">
@@ -48090,7 +48090,7 @@
         <v>277536800</v>
       </c>
       <c r="C133" t="n">
-        <v>720959.1880592573</v>
+        <v>2948986.87548962</v>
       </c>
     </row>
     <row r="134">
@@ -48101,7 +48101,7 @@
         <v>277536800</v>
       </c>
       <c r="C134" t="n">
-        <v>723836.9380592573</v>
+        <v>2951864.62548962</v>
       </c>
     </row>
     <row r="135">
@@ -48112,7 +48112,7 @@
         <v>277536800</v>
       </c>
       <c r="C135" t="n">
-        <v>726714.6880592573</v>
+        <v>2954742.37548962</v>
       </c>
     </row>
     <row r="136">
@@ -48123,7 +48123,7 @@
         <v>277536800</v>
       </c>
       <c r="C136" t="n">
-        <v>729592.4380592573</v>
+        <v>2957620.12548962</v>
       </c>
     </row>
     <row r="137">
@@ -48134,7 +48134,7 @@
         <v>277536800</v>
       </c>
       <c r="C137" t="n">
-        <v>732470.1880592573</v>
+        <v>2960497.87548962</v>
       </c>
     </row>
     <row r="138">
@@ -48145,7 +48145,7 @@
         <v>277536800</v>
       </c>
       <c r="C138" t="n">
-        <v>727008.4888140293</v>
+        <v>2957436.176244393</v>
       </c>
     </row>
     <row r="139">
@@ -48156,7 +48156,7 @@
         <v>277536800</v>
       </c>
       <c r="C139" t="n">
-        <v>719403.5888140292</v>
+        <v>2949831.276244393</v>
       </c>
     </row>
     <row r="140">
@@ -48167,7 +48167,7 @@
         <v>277536800</v>
       </c>
       <c r="C140" t="n">
-        <v>711798.6888140292</v>
+        <v>2942226.376244393</v>
       </c>
     </row>
     <row r="141">
@@ -48178,7 +48178,7 @@
         <v>277536800</v>
       </c>
       <c r="C141" t="n">
-        <v>704193.7888140292</v>
+        <v>2934621.476244393</v>
       </c>
     </row>
     <row r="142">
@@ -48189,7 +48189,7 @@
         <v>277536800</v>
       </c>
       <c r="C142" t="n">
-        <v>699072.4671168614</v>
+        <v>2927100.154547225</v>
       </c>
     </row>
     <row r="143">
@@ -48200,7 +48200,7 @@
         <v>277536800</v>
       </c>
       <c r="C143" t="n">
-        <v>697604.8552168617</v>
+        <v>2925632.542647226</v>
       </c>
     </row>
     <row r="144">
@@ -48211,7 +48211,7 @@
         <v>277536800</v>
       </c>
       <c r="C144" t="n">
-        <v>697604.8552168617</v>
+        <v>2925632.542647226</v>
       </c>
     </row>
     <row r="145">
@@ -48222,7 +48222,7 @@
         <v>277536800</v>
       </c>
       <c r="C145" t="n">
-        <v>697604.8552168617</v>
+        <v>2925632.542647226</v>
       </c>
     </row>
     <row r="146">
@@ -48233,7 +48233,7 @@
         <v>277536800</v>
       </c>
       <c r="C146" t="n">
-        <v>697604.8552168617</v>
+        <v>2925632.542647226</v>
       </c>
     </row>
     <row r="147">
@@ -48244,7 +48244,7 @@
         <v>277536800</v>
       </c>
       <c r="C147" t="n">
-        <v>697604.8552168617</v>
+        <v>2925632.542647226</v>
       </c>
     </row>
     <row r="148">
@@ -48255,7 +48255,7 @@
         <v>277536800</v>
       </c>
       <c r="C148" t="n">
-        <v>696350.7351357434</v>
+        <v>2925632.542647226</v>
       </c>
     </row>
     <row r="149">
@@ -48266,7 +48266,7 @@
         <v>277536800</v>
       </c>
       <c r="C149" t="n">
-        <v>693950.8285064496</v>
+        <v>2923232.636017932</v>
       </c>
     </row>
     <row r="150">
@@ -48277,7 +48277,7 @@
         <v>277536800</v>
       </c>
       <c r="C150" t="n">
-        <v>693155.1120490257</v>
+        <v>2920829.049152884</v>
       </c>
     </row>
     <row r="151">
@@ -48288,7 +48288,7 @@
         <v>277536800</v>
       </c>
       <c r="C151" t="n">
-        <v>690701.7306680339</v>
+        <v>2918375.667771892</v>
       </c>
     </row>
     <row r="152">
@@ -48299,7 +48299,7 @@
         <v>277536800</v>
       </c>
       <c r="C152" t="n">
-        <v>690043.1362505509</v>
+        <v>2914556.010736133</v>
       </c>
     </row>
     <row r="153">
@@ -48310,7 +48310,7 @@
         <v>277536800</v>
       </c>
       <c r="C153" t="n">
-        <v>682438.2362505508</v>
+        <v>2910465.923680915</v>
       </c>
     </row>
     <row r="154">
@@ -48321,7 +48321,7 @@
         <v>277536800</v>
       </c>
       <c r="C154" t="n">
-        <v>685116.6866226149</v>
+        <v>2913144.37405298</v>
       </c>
     </row>
     <row r="155">
@@ -48332,7 +48332,7 @@
         <v>277536800</v>
       </c>
       <c r="C155" t="n">
-        <v>687994.4366226149</v>
+        <v>2916022.12405298</v>
       </c>
     </row>
     <row r="156">
@@ -48343,7 +48343,7 @@
         <v>277536800</v>
       </c>
       <c r="C156" t="n">
-        <v>690872.1866226149</v>
+        <v>2918899.87405298</v>
       </c>
     </row>
     <row r="157">
@@ -48354,7 +48354,7 @@
         <v>277536800</v>
       </c>
       <c r="C157" t="n">
-        <v>693749.9366226149</v>
+        <v>2921777.62405298</v>
       </c>
     </row>
     <row r="158">
@@ -48365,7 +48365,7 @@
         <v>277536800</v>
       </c>
       <c r="C158" t="n">
-        <v>696627.6866226149</v>
+        <v>2924655.37405298</v>
       </c>
     </row>
     <row r="159">
@@ -48376,7 +48376,7 @@
         <v>277536800</v>
       </c>
       <c r="C159" t="n">
-        <v>699505.4366226149</v>
+        <v>2927533.12405298</v>
       </c>
     </row>
     <row r="160">
@@ -48387,7 +48387,7 @@
         <v>277536800</v>
       </c>
       <c r="C160" t="n">
-        <v>702383.1866226149</v>
+        <v>2930410.87405298</v>
       </c>
     </row>
     <row r="161">
@@ -48398,7 +48398,7 @@
         <v>277536800</v>
       </c>
       <c r="C161" t="n">
-        <v>705260.9366226149</v>
+        <v>2933288.62405298</v>
       </c>
     </row>
     <row r="162">
@@ -48409,7 +48409,7 @@
         <v>277536800</v>
       </c>
       <c r="C162" t="n">
-        <v>705260.9366226149</v>
+        <v>2933288.62405298</v>
       </c>
     </row>
     <row r="163">
@@ -48420,7 +48420,7 @@
         <v>277536800</v>
       </c>
       <c r="C163" t="n">
-        <v>697656.0366226148</v>
+        <v>2925683.72405298</v>
       </c>
     </row>
     <row r="164">
@@ -48431,7 +48431,7 @@
         <v>277536800</v>
       </c>
       <c r="C164" t="n">
-        <v>692290.8600460435</v>
+        <v>2920318.547476408</v>
       </c>
     </row>
     <row r="165">
@@ -48442,7 +48442,7 @@
         <v>277536800</v>
       </c>
       <c r="C165" t="n">
-        <v>692177.0564764942</v>
+        <v>2920204.743906859</v>
       </c>
     </row>
     <row r="166">
@@ -48453,7 +48453,7 @@
         <v>277536800</v>
       </c>
       <c r="C166" t="n">
-        <v>692177.0564764942</v>
+        <v>2920204.743906859</v>
       </c>
     </row>
     <row r="167">
@@ -48464,7 +48464,7 @@
         <v>277536800</v>
       </c>
       <c r="C167" t="n">
-        <v>692177.0564764942</v>
+        <v>2920204.743906859</v>
       </c>
     </row>
     <row r="168">
@@ -48475,7 +48475,7 @@
         <v>277536800</v>
       </c>
       <c r="C168" t="n">
-        <v>692177.0564764942</v>
+        <v>2920204.743906859</v>
       </c>
     </row>
     <row r="169">
@@ -48486,7 +48486,7 @@
         <v>277536800</v>
       </c>
       <c r="C169" t="n">
-        <v>692733.0814108214</v>
+        <v>2920204.743906859</v>
       </c>
     </row>
   </sheetData>

--- a/Modelo_España_Portugal/Resultados/ES_PT_Unidos.xlsx
+++ b/Modelo_España_Portugal/Resultados/ES_PT_Unidos.xlsx
@@ -51418,7 +51418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51429,20 +51429,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>carrier</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>generator</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sub_network</t>
         </is>
@@ -51454,22 +51464,28 @@
           <t>ES_electricity_market_bus</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>-3.7038</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40.4168</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>ES_solar</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -51481,18 +51497,24 @@
           <t>ES_water_bus</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>-3.7038</v>
+      </c>
+      <c r="C3" t="n">
+        <v>40.4168</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -51504,22 +51526,28 @@
           <t>ES_gas_bus</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>-3.7038</v>
+      </c>
+      <c r="C4" t="n">
+        <v>40.4168</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>gas</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>ES_gas</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -51531,22 +51559,28 @@
           <t>ES_hydrogen_bus</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>-3.7038</v>
+      </c>
+      <c r="C5" t="n">
+        <v>40.4168</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ES_load_shedding_h2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -51558,22 +51592,28 @@
           <t>ES_SRES_bus</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>-3.7038</v>
+      </c>
+      <c r="C6" t="n">
+        <v>40.4168</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ES_SRES_solar</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -51585,22 +51625,28 @@
           <t>PT_electricity_market_bus</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="n">
+        <v>-9.1393</v>
+      </c>
+      <c r="C7" t="n">
+        <v>38.7223</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>PT_solar</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -51612,18 +51658,24 @@
           <t>PT_water_bus</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>-9.1393</v>
+      </c>
+      <c r="C8" t="n">
+        <v>38.7223</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -51635,22 +51687,28 @@
           <t>PT_gas_bus</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>-9.1393</v>
+      </c>
+      <c r="C9" t="n">
+        <v>38.7223</v>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>gas</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>PT_gas</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -51662,22 +51720,28 @@
           <t>PT_hydrogen_bus</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="n">
+        <v>-9.1393</v>
+      </c>
+      <c r="C10" t="n">
+        <v>38.7223</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>PT_load_shedding_h2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -51689,22 +51753,28 @@
           <t>PT_SRES_bus</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="n">
+        <v>-9.1393</v>
+      </c>
+      <c r="C11" t="n">
+        <v>38.7223</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>PT_SRES_solar</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>9</t>
         </is>

--- a/Modelo_España_Portugal/Resultados/ES_PT_Unidos.xlsx
+++ b/Modelo_España_Portugal/Resultados/ES_PT_Unidos.xlsx
@@ -59362,7 +59362,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -59380,7 +59380,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="14">
